--- a/resources/report/60/95/ex_imp/TID_111_VAT_INVOICE_IMP.xlsx
+++ b/resources/report/60/95/ex_imp/TID_111_VAT_INVOICE_IMP.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28429"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lvthe\OneDrive\Máy tính\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7E4D0DD-E5E7-4A59-A8D5-98C00ED54998}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E82D2212-20BA-458B-9B1F-006070F08A1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -657,14 +657,14 @@
     <t xml:space="preserve">asdasdasd </t>
   </si>
   <si>
-    <t>adsdassa</t>
+    <t>asdasd</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="55" x14ac:knownFonts="1">
+  <fonts count="54" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -998,13 +998,6 @@
     <font>
       <sz val="12"/>
       <color theme="4"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color rgb="FF0070C0"/>
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
@@ -1563,7 +1556,7 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyFont="0" applyBorder="0"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyFont="0"/>
   </cellStyleXfs>
-  <cellXfs count="143">
+  <cellXfs count="144">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1841,6 +1834,114 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="53" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="14" fontId="45" fillId="18" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="45" fillId="18" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="18" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="18" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="18" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="18" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="18" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="18" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="26" fillId="18" borderId="18" xfId="24" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="26" fillId="18" borderId="19" xfId="24" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="26" fillId="18" borderId="20" xfId="24" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="26" fillId="18" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="26" fillId="18" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="18" borderId="18" xfId="24" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="18" borderId="20" xfId="24" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="18" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="18" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="18" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="27" fillId="18" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1850,9 +1951,6 @@
     <xf numFmtId="0" fontId="8" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="39" fillId="18" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1865,118 +1963,18 @@
     <xf numFmtId="0" fontId="8" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="26" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="42" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="18" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="18" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="18" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="18" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="18" borderId="18" xfId="24" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="18" borderId="20" xfId="24" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="18" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="18" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="18" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="18" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="18" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="26" fillId="18" borderId="18" xfId="24" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="26" fillId="18" borderId="19" xfId="24" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="26" fillId="18" borderId="20" xfId="24" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="26" fillId="18" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="26" fillId="18" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="18" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="18" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="45" fillId="18" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="49" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="45" fillId="18" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="18" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="18" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="50" fillId="18" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="43">
     <cellStyle name="20% - Accent1" xfId="1" builtinId="30" customBuiltin="1"/>
@@ -2356,22 +2354,22 @@
       <c r="E2" s="35"/>
       <c r="F2" s="35"/>
       <c r="G2" s="35"/>
-      <c r="H2" s="101" t="s">
+      <c r="H2" s="136" t="s">
         <v>13</v>
       </c>
-      <c r="I2" s="101"/>
-      <c r="J2" s="101"/>
-      <c r="K2" s="101"/>
-      <c r="L2" s="101"/>
-      <c r="M2" s="101"/>
-      <c r="N2" s="101"/>
-      <c r="O2" s="101"/>
-      <c r="P2" s="102" t="s">
+      <c r="I2" s="136"/>
+      <c r="J2" s="136"/>
+      <c r="K2" s="136"/>
+      <c r="L2" s="136"/>
+      <c r="M2" s="136"/>
+      <c r="N2" s="136"/>
+      <c r="O2" s="136"/>
+      <c r="P2" s="137" t="s">
         <v>42</v>
       </c>
-      <c r="Q2" s="102"/>
-      <c r="R2" s="102"/>
-      <c r="S2" s="102"/>
+      <c r="Q2" s="137"/>
+      <c r="R2" s="137"/>
+      <c r="S2" s="137"/>
       <c r="T2" s="36"/>
       <c r="U2" s="11"/>
     </row>
@@ -2383,22 +2381,22 @@
       <c r="E3" s="38"/>
       <c r="F3" s="38"/>
       <c r="G3" s="38"/>
-      <c r="H3" s="103" t="s">
+      <c r="H3" s="138" t="s">
         <v>33</v>
       </c>
-      <c r="I3" s="103"/>
-      <c r="J3" s="103"/>
-      <c r="K3" s="103"/>
-      <c r="L3" s="103"/>
-      <c r="M3" s="103"/>
-      <c r="N3" s="103"/>
-      <c r="O3" s="103"/>
-      <c r="P3" s="104" t="s">
+      <c r="I3" s="138"/>
+      <c r="J3" s="138"/>
+      <c r="K3" s="138"/>
+      <c r="L3" s="138"/>
+      <c r="M3" s="138"/>
+      <c r="N3" s="138"/>
+      <c r="O3" s="138"/>
+      <c r="P3" s="139" t="s">
         <v>43</v>
       </c>
-      <c r="Q3" s="104"/>
-      <c r="R3" s="104"/>
-      <c r="S3" s="104"/>
+      <c r="Q3" s="139"/>
+      <c r="R3" s="139"/>
+      <c r="S3" s="139"/>
       <c r="T3" s="39"/>
       <c r="U3" s="12"/>
     </row>
@@ -2410,14 +2408,14 @@
       <c r="E4" s="38"/>
       <c r="F4" s="38"/>
       <c r="G4" s="38"/>
-      <c r="H4" s="105"/>
-      <c r="I4" s="105"/>
-      <c r="J4" s="105"/>
-      <c r="K4" s="105"/>
-      <c r="L4" s="105"/>
-      <c r="M4" s="105"/>
-      <c r="N4" s="105"/>
-      <c r="O4" s="105"/>
+      <c r="H4" s="100"/>
+      <c r="I4" s="100"/>
+      <c r="J4" s="100"/>
+      <c r="K4" s="100"/>
+      <c r="L4" s="100"/>
+      <c r="M4" s="100"/>
+      <c r="N4" s="100"/>
+      <c r="O4" s="100"/>
       <c r="P4" s="40"/>
       <c r="Q4" s="40"/>
       <c r="R4" s="40"/>
@@ -2433,15 +2431,15 @@
       <c r="E5" s="38"/>
       <c r="F5" s="38"/>
       <c r="G5" s="38"/>
-      <c r="H5" s="106" t="s">
+      <c r="H5" s="140" t="s">
         <v>45</v>
       </c>
-      <c r="I5" s="106"/>
-      <c r="J5" s="106"/>
-      <c r="K5" s="106"/>
-      <c r="L5" s="106"/>
-      <c r="M5" s="106"/>
-      <c r="N5" s="106"/>
+      <c r="I5" s="140"/>
+      <c r="J5" s="140"/>
+      <c r="K5" s="140"/>
+      <c r="L5" s="140"/>
+      <c r="M5" s="140"/>
+      <c r="N5" s="140"/>
       <c r="O5" s="40"/>
       <c r="P5" s="40"/>
       <c r="Q5" s="40"/>
@@ -2483,14 +2481,14 @@
         <v>46</v>
       </c>
       <c r="G7" s="75"/>
-      <c r="H7" s="107"/>
-      <c r="I7" s="107"/>
-      <c r="J7" s="107"/>
-      <c r="K7" s="107"/>
-      <c r="L7" s="107"/>
-      <c r="M7" s="107"/>
-      <c r="N7" s="107"/>
-      <c r="O7" s="107"/>
+      <c r="H7" s="141"/>
+      <c r="I7" s="141"/>
+      <c r="J7" s="141"/>
+      <c r="K7" s="141"/>
+      <c r="L7" s="141"/>
+      <c r="M7" s="141"/>
+      <c r="N7" s="141"/>
+      <c r="O7" s="141"/>
       <c r="P7" s="94"/>
       <c r="Q7" s="94"/>
       <c r="R7" s="38"/>
@@ -2533,19 +2531,19 @@
       <c r="G9" s="95" t="s">
         <v>16</v>
       </c>
-      <c r="H9" s="97"/>
-      <c r="I9" s="97"/>
-      <c r="J9" s="97"/>
-      <c r="K9" s="97"/>
-      <c r="L9" s="97"/>
-      <c r="M9" s="97"/>
-      <c r="N9" s="97"/>
-      <c r="O9" s="97"/>
-      <c r="P9" s="97"/>
-      <c r="Q9" s="97"/>
-      <c r="R9" s="97"/>
-      <c r="S9" s="97"/>
-      <c r="T9" s="97"/>
+      <c r="H9" s="133"/>
+      <c r="I9" s="133"/>
+      <c r="J9" s="133"/>
+      <c r="K9" s="133"/>
+      <c r="L9" s="133"/>
+      <c r="M9" s="133"/>
+      <c r="N9" s="133"/>
+      <c r="O9" s="133"/>
+      <c r="P9" s="133"/>
+      <c r="Q9" s="133"/>
+      <c r="R9" s="133"/>
+      <c r="S9" s="133"/>
+      <c r="T9" s="133"/>
       <c r="U9" s="14"/>
     </row>
     <row r="10" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -2560,19 +2558,19 @@
       <c r="G10" s="38" t="s">
         <v>16</v>
       </c>
-      <c r="H10" s="98"/>
-      <c r="I10" s="98"/>
-      <c r="J10" s="98"/>
-      <c r="K10" s="98"/>
-      <c r="L10" s="98"/>
-      <c r="M10" s="98"/>
-      <c r="N10" s="98"/>
-      <c r="O10" s="98"/>
-      <c r="P10" s="98"/>
-      <c r="Q10" s="98"/>
-      <c r="R10" s="98"/>
-      <c r="S10" s="98"/>
-      <c r="T10" s="98"/>
+      <c r="H10" s="134"/>
+      <c r="I10" s="134"/>
+      <c r="J10" s="134"/>
+      <c r="K10" s="134"/>
+      <c r="L10" s="134"/>
+      <c r="M10" s="134"/>
+      <c r="N10" s="134"/>
+      <c r="O10" s="134"/>
+      <c r="P10" s="134"/>
+      <c r="Q10" s="134"/>
+      <c r="R10" s="134"/>
+      <c r="S10" s="134"/>
+      <c r="T10" s="134"/>
       <c r="U10" s="12"/>
     </row>
     <row r="11" spans="1:21" ht="25.15" customHeight="1" x14ac:dyDescent="0.2">
@@ -2587,19 +2585,19 @@
       <c r="G11" s="38" t="s">
         <v>16</v>
       </c>
-      <c r="H11" s="99"/>
-      <c r="I11" s="99"/>
-      <c r="J11" s="99"/>
-      <c r="K11" s="99"/>
-      <c r="L11" s="99"/>
-      <c r="M11" s="99"/>
-      <c r="N11" s="99"/>
-      <c r="O11" s="99"/>
-      <c r="P11" s="99"/>
-      <c r="Q11" s="99"/>
-      <c r="R11" s="99"/>
-      <c r="S11" s="99"/>
-      <c r="T11" s="99"/>
+      <c r="H11" s="135"/>
+      <c r="I11" s="135"/>
+      <c r="J11" s="135"/>
+      <c r="K11" s="135"/>
+      <c r="L11" s="135"/>
+      <c r="M11" s="135"/>
+      <c r="N11" s="135"/>
+      <c r="O11" s="135"/>
+      <c r="P11" s="135"/>
+      <c r="Q11" s="135"/>
+      <c r="R11" s="135"/>
+      <c r="S11" s="135"/>
+      <c r="T11" s="135"/>
       <c r="U11" s="12"/>
     </row>
     <row r="12" spans="1:21" ht="15.4" customHeight="1" x14ac:dyDescent="0.25">
@@ -2614,11 +2612,11 @@
       <c r="G12" s="38" t="s">
         <v>16</v>
       </c>
-      <c r="H12" s="100"/>
-      <c r="I12" s="100"/>
-      <c r="J12" s="100"/>
-      <c r="K12" s="100"/>
-      <c r="L12" s="100"/>
+      <c r="H12" s="128"/>
+      <c r="I12" s="128"/>
+      <c r="J12" s="128"/>
+      <c r="K12" s="128"/>
+      <c r="L12" s="128"/>
       <c r="M12" s="42"/>
       <c r="N12" s="42"/>
       <c r="O12" s="42"/>
@@ -2641,19 +2639,19 @@
       <c r="G13" s="38" t="s">
         <v>16</v>
       </c>
-      <c r="H13" s="100"/>
-      <c r="I13" s="100"/>
-      <c r="J13" s="100"/>
-      <c r="K13" s="100"/>
-      <c r="L13" s="100"/>
-      <c r="M13" s="100"/>
-      <c r="N13" s="100"/>
-      <c r="O13" s="100"/>
-      <c r="P13" s="100"/>
-      <c r="Q13" s="100"/>
-      <c r="R13" s="100"/>
-      <c r="S13" s="100"/>
-      <c r="T13" s="100"/>
+      <c r="H13" s="128"/>
+      <c r="I13" s="128"/>
+      <c r="J13" s="128"/>
+      <c r="K13" s="128"/>
+      <c r="L13" s="128"/>
+      <c r="M13" s="128"/>
+      <c r="N13" s="128"/>
+      <c r="O13" s="128"/>
+      <c r="P13" s="128"/>
+      <c r="Q13" s="128"/>
+      <c r="R13" s="128"/>
+      <c r="S13" s="128"/>
+      <c r="T13" s="128"/>
       <c r="U13" s="13"/>
     </row>
     <row r="14" spans="1:21" ht="13.15" customHeight="1" x14ac:dyDescent="0.2">
@@ -2664,19 +2662,19 @@
       <c r="E14" s="38"/>
       <c r="F14" s="38"/>
       <c r="G14" s="38"/>
-      <c r="H14" s="108"/>
-      <c r="I14" s="108"/>
-      <c r="J14" s="108"/>
-      <c r="K14" s="108"/>
-      <c r="L14" s="108"/>
-      <c r="M14" s="108"/>
-      <c r="N14" s="108"/>
-      <c r="O14" s="108"/>
-      <c r="P14" s="108"/>
-      <c r="Q14" s="108"/>
-      <c r="R14" s="108"/>
-      <c r="S14" s="108"/>
-      <c r="T14" s="108"/>
+      <c r="H14" s="129"/>
+      <c r="I14" s="129"/>
+      <c r="J14" s="129"/>
+      <c r="K14" s="129"/>
+      <c r="L14" s="129"/>
+      <c r="M14" s="129"/>
+      <c r="N14" s="129"/>
+      <c r="O14" s="129"/>
+      <c r="P14" s="129"/>
+      <c r="Q14" s="129"/>
+      <c r="R14" s="129"/>
+      <c r="S14" s="129"/>
+      <c r="T14" s="129"/>
       <c r="U14" s="13"/>
     </row>
     <row r="15" spans="1:21" ht="4.9000000000000004" customHeight="1" x14ac:dyDescent="0.2">
@@ -2737,19 +2735,19 @@
       <c r="E17" s="41"/>
       <c r="F17" s="41"/>
       <c r="G17" s="41"/>
-      <c r="H17" s="111"/>
-      <c r="I17" s="111"/>
-      <c r="J17" s="111"/>
-      <c r="K17" s="111"/>
-      <c r="L17" s="111"/>
-      <c r="M17" s="111"/>
-      <c r="N17" s="111"/>
-      <c r="O17" s="111"/>
-      <c r="P17" s="111"/>
-      <c r="Q17" s="111"/>
-      <c r="R17" s="111"/>
-      <c r="S17" s="111"/>
-      <c r="T17" s="111"/>
+      <c r="H17" s="132"/>
+      <c r="I17" s="132"/>
+      <c r="J17" s="132"/>
+      <c r="K17" s="132"/>
+      <c r="L17" s="132"/>
+      <c r="M17" s="132"/>
+      <c r="N17" s="132"/>
+      <c r="O17" s="132"/>
+      <c r="P17" s="132"/>
+      <c r="Q17" s="132"/>
+      <c r="R17" s="132"/>
+      <c r="S17" s="132"/>
+      <c r="T17" s="132"/>
       <c r="U17" s="15"/>
     </row>
     <row r="18" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -2784,22 +2782,22 @@
       </c>
       <c r="C19" s="41"/>
       <c r="D19" s="41"/>
-      <c r="E19" s="100"/>
-      <c r="F19" s="100"/>
-      <c r="G19" s="100"/>
-      <c r="H19" s="100"/>
-      <c r="I19" s="100"/>
-      <c r="J19" s="100"/>
-      <c r="K19" s="100"/>
-      <c r="L19" s="100"/>
-      <c r="M19" s="100"/>
-      <c r="N19" s="100"/>
-      <c r="O19" s="100"/>
-      <c r="P19" s="100"/>
-      <c r="Q19" s="100"/>
-      <c r="R19" s="100"/>
-      <c r="S19" s="100"/>
-      <c r="T19" s="100"/>
+      <c r="E19" s="128"/>
+      <c r="F19" s="128"/>
+      <c r="G19" s="128"/>
+      <c r="H19" s="128"/>
+      <c r="I19" s="128"/>
+      <c r="J19" s="128"/>
+      <c r="K19" s="128"/>
+      <c r="L19" s="128"/>
+      <c r="M19" s="128"/>
+      <c r="N19" s="128"/>
+      <c r="O19" s="128"/>
+      <c r="P19" s="128"/>
+      <c r="Q19" s="128"/>
+      <c r="R19" s="128"/>
+      <c r="S19" s="128"/>
+      <c r="T19" s="128"/>
       <c r="U19" s="15"/>
     </row>
     <row r="20" spans="1:21" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
@@ -2839,9 +2837,9 @@
       <c r="G21" s="41"/>
       <c r="H21" s="38"/>
       <c r="I21" s="38"/>
-      <c r="J21" s="110"/>
-      <c r="K21" s="110"/>
-      <c r="L21" s="110"/>
+      <c r="J21" s="131"/>
+      <c r="K21" s="131"/>
+      <c r="L21" s="131"/>
       <c r="M21" s="38"/>
       <c r="N21" s="38"/>
       <c r="O21" s="38"/>
@@ -2907,34 +2905,34 @@
       <c r="B24" s="54" t="s">
         <v>0</v>
       </c>
-      <c r="C24" s="109" t="s">
+      <c r="C24" s="130" t="s">
         <v>2</v>
       </c>
-      <c r="D24" s="109"/>
-      <c r="E24" s="109"/>
-      <c r="F24" s="109"/>
-      <c r="G24" s="109"/>
-      <c r="H24" s="109"/>
-      <c r="I24" s="109"/>
-      <c r="J24" s="109"/>
-      <c r="K24" s="109"/>
+      <c r="D24" s="130"/>
+      <c r="E24" s="130"/>
+      <c r="F24" s="130"/>
+      <c r="G24" s="130"/>
+      <c r="H24" s="130"/>
+      <c r="I24" s="130"/>
+      <c r="J24" s="130"/>
+      <c r="K24" s="130"/>
       <c r="L24" s="83" t="s">
         <v>31</v>
       </c>
-      <c r="M24" s="109" t="s">
+      <c r="M24" s="130" t="s">
         <v>4</v>
       </c>
-      <c r="N24" s="109"/>
-      <c r="O24" s="109"/>
-      <c r="P24" s="109" t="s">
+      <c r="N24" s="130"/>
+      <c r="O24" s="130"/>
+      <c r="P24" s="130" t="s">
         <v>5</v>
       </c>
-      <c r="Q24" s="109"/>
-      <c r="R24" s="109"/>
-      <c r="S24" s="109" t="s">
+      <c r="Q24" s="130"/>
+      <c r="R24" s="130"/>
+      <c r="S24" s="130" t="s">
         <v>7</v>
       </c>
-      <c r="T24" s="109"/>
+      <c r="T24" s="130"/>
       <c r="U24" s="16"/>
     </row>
     <row r="25" spans="1:21" s="4" customFormat="1" ht="13.15" customHeight="1" x14ac:dyDescent="0.2">
@@ -2942,34 +2940,34 @@
       <c r="B25" s="84" t="s">
         <v>1</v>
       </c>
-      <c r="C25" s="112" t="s">
+      <c r="C25" s="126" t="s">
         <v>17</v>
       </c>
-      <c r="D25" s="112"/>
-      <c r="E25" s="112"/>
-      <c r="F25" s="112"/>
-      <c r="G25" s="112"/>
-      <c r="H25" s="112"/>
-      <c r="I25" s="112"/>
-      <c r="J25" s="112"/>
-      <c r="K25" s="112"/>
+      <c r="D25" s="126"/>
+      <c r="E25" s="126"/>
+      <c r="F25" s="126"/>
+      <c r="G25" s="126"/>
+      <c r="H25" s="126"/>
+      <c r="I25" s="126"/>
+      <c r="J25" s="126"/>
+      <c r="K25" s="126"/>
       <c r="L25" s="84" t="s">
         <v>3</v>
       </c>
-      <c r="M25" s="112" t="s">
+      <c r="M25" s="126" t="s">
         <v>14</v>
       </c>
-      <c r="N25" s="112"/>
-      <c r="O25" s="112"/>
-      <c r="P25" s="112" t="s">
+      <c r="N25" s="126"/>
+      <c r="O25" s="126"/>
+      <c r="P25" s="126" t="s">
         <v>6</v>
       </c>
-      <c r="Q25" s="112"/>
-      <c r="R25" s="112"/>
-      <c r="S25" s="112" t="s">
+      <c r="Q25" s="126"/>
+      <c r="R25" s="126"/>
+      <c r="S25" s="126" t="s">
         <v>8</v>
       </c>
-      <c r="T25" s="112"/>
+      <c r="T25" s="126"/>
       <c r="U25" s="17"/>
     </row>
     <row r="26" spans="1:21" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -2977,57 +2975,57 @@
       <c r="B26" s="85">
         <v>1</v>
       </c>
-      <c r="C26" s="113">
+      <c r="C26" s="127">
         <v>2</v>
       </c>
-      <c r="D26" s="113"/>
-      <c r="E26" s="113"/>
-      <c r="F26" s="113"/>
-      <c r="G26" s="113"/>
-      <c r="H26" s="113"/>
-      <c r="I26" s="113"/>
-      <c r="J26" s="113"/>
-      <c r="K26" s="113"/>
+      <c r="D26" s="127"/>
+      <c r="E26" s="127"/>
+      <c r="F26" s="127"/>
+      <c r="G26" s="127"/>
+      <c r="H26" s="127"/>
+      <c r="I26" s="127"/>
+      <c r="J26" s="127"/>
+      <c r="K26" s="127"/>
       <c r="L26" s="85">
         <v>3</v>
       </c>
-      <c r="M26" s="113">
+      <c r="M26" s="127">
         <v>4</v>
       </c>
-      <c r="N26" s="113"/>
-      <c r="O26" s="113"/>
-      <c r="P26" s="113">
+      <c r="N26" s="127"/>
+      <c r="O26" s="127"/>
+      <c r="P26" s="127">
         <v>5</v>
       </c>
-      <c r="Q26" s="113"/>
-      <c r="R26" s="113"/>
-      <c r="S26" s="113" t="s">
+      <c r="Q26" s="127"/>
+      <c r="R26" s="127"/>
+      <c r="S26" s="127" t="s">
         <v>18</v>
       </c>
-      <c r="T26" s="113"/>
+      <c r="T26" s="127"/>
       <c r="U26" s="18"/>
     </row>
     <row r="27" spans="1:21" s="3" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="57"/>
       <c r="B27" s="89"/>
-      <c r="C27" s="123"/>
-      <c r="D27" s="124"/>
-      <c r="E27" s="124"/>
-      <c r="F27" s="124"/>
-      <c r="G27" s="124"/>
-      <c r="H27" s="124"/>
-      <c r="I27" s="124"/>
-      <c r="J27" s="124"/>
-      <c r="K27" s="125"/>
+      <c r="C27" s="110"/>
+      <c r="D27" s="111"/>
+      <c r="E27" s="111"/>
+      <c r="F27" s="111"/>
+      <c r="G27" s="111"/>
+      <c r="H27" s="111"/>
+      <c r="I27" s="111"/>
+      <c r="J27" s="111"/>
+      <c r="K27" s="112"/>
       <c r="L27" s="90"/>
-      <c r="M27" s="126"/>
-      <c r="N27" s="127"/>
-      <c r="O27" s="128"/>
-      <c r="P27" s="126"/>
-      <c r="Q27" s="127"/>
-      <c r="R27" s="128"/>
-      <c r="S27" s="129"/>
-      <c r="T27" s="130"/>
+      <c r="M27" s="113"/>
+      <c r="N27" s="114"/>
+      <c r="O27" s="115"/>
+      <c r="P27" s="113"/>
+      <c r="Q27" s="114"/>
+      <c r="R27" s="115"/>
+      <c r="S27" s="116"/>
+      <c r="T27" s="117"/>
       <c r="U27" s="30"/>
     </row>
     <row r="28" spans="1:21" s="6" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
@@ -3042,44 +3040,44 @@
       <c r="I28" s="60"/>
       <c r="J28" s="60"/>
       <c r="K28" s="60"/>
-      <c r="L28" s="114" t="s">
+      <c r="L28" s="120" t="s">
         <v>38</v>
       </c>
-      <c r="M28" s="114"/>
-      <c r="N28" s="114"/>
-      <c r="O28" s="114"/>
-      <c r="P28" s="114"/>
-      <c r="Q28" s="114"/>
-      <c r="R28" s="115"/>
-      <c r="S28" s="116"/>
-      <c r="T28" s="117"/>
+      <c r="M28" s="120"/>
+      <c r="N28" s="120"/>
+      <c r="O28" s="120"/>
+      <c r="P28" s="120"/>
+      <c r="Q28" s="120"/>
+      <c r="R28" s="121"/>
+      <c r="S28" s="122"/>
+      <c r="T28" s="123"/>
       <c r="U28" s="31"/>
     </row>
     <row r="29" spans="1:21" s="6" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="57"/>
-      <c r="B29" s="131" t="s">
+      <c r="B29" s="118" t="s">
         <v>20</v>
       </c>
-      <c r="C29" s="132"/>
-      <c r="D29" s="132"/>
-      <c r="E29" s="132"/>
-      <c r="F29" s="132"/>
-      <c r="G29" s="132"/>
-      <c r="H29" s="132"/>
+      <c r="C29" s="119"/>
+      <c r="D29" s="119"/>
+      <c r="E29" s="119"/>
+      <c r="F29" s="119"/>
+      <c r="G29" s="119"/>
+      <c r="H29" s="119"/>
       <c r="I29" s="87"/>
       <c r="J29" s="61"/>
       <c r="K29" s="87"/>
-      <c r="L29" s="114" t="s">
+      <c r="L29" s="120" t="s">
         <v>39</v>
       </c>
-      <c r="M29" s="114"/>
-      <c r="N29" s="114"/>
-      <c r="O29" s="114"/>
-      <c r="P29" s="114"/>
-      <c r="Q29" s="114"/>
-      <c r="R29" s="115"/>
-      <c r="S29" s="116"/>
-      <c r="T29" s="117"/>
+      <c r="M29" s="120"/>
+      <c r="N29" s="120"/>
+      <c r="O29" s="120"/>
+      <c r="P29" s="120"/>
+      <c r="Q29" s="120"/>
+      <c r="R29" s="121"/>
+      <c r="S29" s="122"/>
+      <c r="T29" s="123"/>
       <c r="U29" s="31"/>
     </row>
     <row r="30" spans="1:21" s="6" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
@@ -3094,17 +3092,17 @@
       <c r="I30" s="87"/>
       <c r="J30" s="87"/>
       <c r="K30" s="87"/>
-      <c r="L30" s="114" t="s">
+      <c r="L30" s="120" t="s">
         <v>40</v>
       </c>
-      <c r="M30" s="114"/>
-      <c r="N30" s="114"/>
-      <c r="O30" s="114"/>
-      <c r="P30" s="114"/>
-      <c r="Q30" s="114"/>
-      <c r="R30" s="115"/>
-      <c r="S30" s="116"/>
-      <c r="T30" s="117"/>
+      <c r="M30" s="120"/>
+      <c r="N30" s="120"/>
+      <c r="O30" s="120"/>
+      <c r="P30" s="120"/>
+      <c r="Q30" s="120"/>
+      <c r="R30" s="121"/>
+      <c r="S30" s="122"/>
+      <c r="T30" s="123"/>
       <c r="U30" s="31"/>
     </row>
     <row r="31" spans="1:21" s="6" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
@@ -3118,18 +3116,18 @@
       <c r="F31" s="44"/>
       <c r="G31" s="44"/>
       <c r="H31" s="44"/>
-      <c r="I31" s="136"/>
-      <c r="J31" s="136"/>
-      <c r="K31" s="136"/>
-      <c r="L31" s="136"/>
-      <c r="M31" s="136"/>
-      <c r="N31" s="136"/>
-      <c r="O31" s="136"/>
-      <c r="P31" s="136"/>
-      <c r="Q31" s="136"/>
-      <c r="R31" s="136"/>
-      <c r="S31" s="136"/>
-      <c r="T31" s="137"/>
+      <c r="I31" s="101"/>
+      <c r="J31" s="101"/>
+      <c r="K31" s="101"/>
+      <c r="L31" s="101"/>
+      <c r="M31" s="101"/>
+      <c r="N31" s="101"/>
+      <c r="O31" s="101"/>
+      <c r="P31" s="101"/>
+      <c r="Q31" s="101"/>
+      <c r="R31" s="101"/>
+      <c r="S31" s="101"/>
+      <c r="T31" s="102"/>
       <c r="U31" s="19"/>
     </row>
     <row r="32" spans="1:21" ht="4.9000000000000004" customHeight="1" x14ac:dyDescent="0.2">
@@ -3158,82 +3156,82 @@
     <row r="33" spans="1:21" s="7" customFormat="1" ht="15.4" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="66"/>
       <c r="B33" s="67"/>
-      <c r="C33" s="120" t="s">
+      <c r="C33" s="107" t="s">
         <v>19</v>
       </c>
-      <c r="D33" s="120"/>
-      <c r="E33" s="120"/>
-      <c r="F33" s="120"/>
-      <c r="G33" s="120"/>
-      <c r="H33" s="120"/>
-      <c r="I33" s="120"/>
-      <c r="J33" s="120"/>
-      <c r="K33" s="120"/>
-      <c r="L33" s="120"/>
-      <c r="M33" s="120"/>
-      <c r="N33" s="120" t="s">
+      <c r="D33" s="107"/>
+      <c r="E33" s="107"/>
+      <c r="F33" s="107"/>
+      <c r="G33" s="107"/>
+      <c r="H33" s="107"/>
+      <c r="I33" s="107"/>
+      <c r="J33" s="107"/>
+      <c r="K33" s="107"/>
+      <c r="L33" s="107"/>
+      <c r="M33" s="107"/>
+      <c r="N33" s="107" t="s">
         <v>35</v>
       </c>
-      <c r="O33" s="120"/>
-      <c r="P33" s="120"/>
-      <c r="Q33" s="120"/>
-      <c r="R33" s="120"/>
-      <c r="S33" s="120"/>
-      <c r="T33" s="120"/>
+      <c r="O33" s="107"/>
+      <c r="P33" s="107"/>
+      <c r="Q33" s="107"/>
+      <c r="R33" s="107"/>
+      <c r="S33" s="107"/>
+      <c r="T33" s="107"/>
       <c r="U33" s="21"/>
     </row>
     <row r="34" spans="1:21" s="8" customFormat="1" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="68"/>
       <c r="B34" s="69"/>
-      <c r="C34" s="121" t="s">
+      <c r="C34" s="108" t="s">
         <v>9</v>
       </c>
-      <c r="D34" s="121"/>
-      <c r="E34" s="121"/>
-      <c r="F34" s="121"/>
-      <c r="G34" s="121"/>
-      <c r="H34" s="121"/>
-      <c r="I34" s="121"/>
-      <c r="J34" s="121"/>
-      <c r="K34" s="121"/>
-      <c r="L34" s="121"/>
-      <c r="M34" s="121"/>
-      <c r="N34" s="121" t="s">
+      <c r="D34" s="108"/>
+      <c r="E34" s="108"/>
+      <c r="F34" s="108"/>
+      <c r="G34" s="108"/>
+      <c r="H34" s="108"/>
+      <c r="I34" s="108"/>
+      <c r="J34" s="108"/>
+      <c r="K34" s="108"/>
+      <c r="L34" s="108"/>
+      <c r="M34" s="108"/>
+      <c r="N34" s="108" t="s">
         <v>9</v>
       </c>
-      <c r="O34" s="121"/>
-      <c r="P34" s="121"/>
-      <c r="Q34" s="121"/>
-      <c r="R34" s="121"/>
-      <c r="S34" s="121"/>
-      <c r="T34" s="121"/>
+      <c r="O34" s="108"/>
+      <c r="P34" s="108"/>
+      <c r="Q34" s="108"/>
+      <c r="R34" s="108"/>
+      <c r="S34" s="108"/>
+      <c r="T34" s="108"/>
       <c r="U34" s="22"/>
     </row>
     <row r="35" spans="1:21" s="9" customFormat="1" ht="15.4" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="55"/>
       <c r="B35" s="70"/>
-      <c r="C35" s="122" t="s">
+      <c r="C35" s="109" t="s">
         <v>10</v>
       </c>
-      <c r="D35" s="122"/>
-      <c r="E35" s="122"/>
-      <c r="F35" s="122"/>
-      <c r="G35" s="122"/>
-      <c r="H35" s="122"/>
-      <c r="I35" s="122"/>
-      <c r="J35" s="122"/>
-      <c r="K35" s="122"/>
-      <c r="L35" s="122"/>
-      <c r="M35" s="122"/>
-      <c r="N35" s="122" t="s">
+      <c r="D35" s="109"/>
+      <c r="E35" s="109"/>
+      <c r="F35" s="109"/>
+      <c r="G35" s="109"/>
+      <c r="H35" s="109"/>
+      <c r="I35" s="109"/>
+      <c r="J35" s="109"/>
+      <c r="K35" s="109"/>
+      <c r="L35" s="109"/>
+      <c r="M35" s="109"/>
+      <c r="N35" s="109" t="s">
         <v>10</v>
       </c>
-      <c r="O35" s="122"/>
-      <c r="P35" s="122"/>
-      <c r="Q35" s="122"/>
-      <c r="R35" s="122"/>
-      <c r="S35" s="122"/>
-      <c r="T35" s="122"/>
+      <c r="O35" s="109"/>
+      <c r="P35" s="109"/>
+      <c r="Q35" s="109"/>
+      <c r="R35" s="109"/>
+      <c r="S35" s="109"/>
+      <c r="T35" s="109"/>
       <c r="U35" s="23"/>
     </row>
     <row r="36" spans="1:21" ht="10.15" customHeight="1" x14ac:dyDescent="0.2">
@@ -3278,10 +3276,10 @@
       </c>
       <c r="O37" s="71"/>
       <c r="P37" s="71"/>
-      <c r="Q37" s="118"/>
-      <c r="R37" s="118"/>
-      <c r="S37" s="118"/>
-      <c r="T37" s="119"/>
+      <c r="Q37" s="124"/>
+      <c r="R37" s="124"/>
+      <c r="S37" s="124"/>
+      <c r="T37" s="125"/>
       <c r="U37" s="25"/>
     </row>
     <row r="38" spans="1:21" s="10" customFormat="1" ht="22.15" customHeight="1" x14ac:dyDescent="0.2">
@@ -3298,15 +3296,15 @@
       <c r="K38" s="74"/>
       <c r="L38" s="74"/>
       <c r="M38" s="73"/>
-      <c r="N38" s="138" t="s">
+      <c r="N38" s="103" t="s">
         <v>41</v>
       </c>
-      <c r="O38" s="139"/>
-      <c r="P38" s="139"/>
-      <c r="Q38" s="140"/>
-      <c r="R38" s="140"/>
-      <c r="S38" s="140"/>
-      <c r="T38" s="141"/>
+      <c r="O38" s="104"/>
+      <c r="P38" s="104"/>
+      <c r="Q38" s="105"/>
+      <c r="R38" s="105"/>
+      <c r="S38" s="105"/>
+      <c r="T38" s="106"/>
       <c r="U38" s="26"/>
     </row>
     <row r="39" spans="1:21" ht="13.15" customHeight="1" x14ac:dyDescent="0.2">
@@ -3330,10 +3328,10 @@
       </c>
       <c r="O39" s="93"/>
       <c r="P39" s="76"/>
-      <c r="Q39" s="133"/>
-      <c r="R39" s="133"/>
-      <c r="S39" s="133"/>
-      <c r="T39" s="134"/>
+      <c r="Q39" s="97"/>
+      <c r="R39" s="97"/>
+      <c r="S39" s="97"/>
+      <c r="T39" s="98"/>
       <c r="U39" s="27"/>
     </row>
     <row r="40" spans="1:21" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
@@ -3369,12 +3367,12 @@
       <c r="E41" s="80"/>
       <c r="F41" s="80"/>
       <c r="G41" s="80"/>
-      <c r="H41" s="80"/>
-      <c r="I41" s="142" t="s">
+      <c r="H41" s="143" t="s">
         <v>50</v>
       </c>
-      <c r="J41" s="96"/>
-      <c r="K41" s="96"/>
+      <c r="I41" s="142"/>
+      <c r="J41" s="142"/>
+      <c r="K41" s="142"/>
       <c r="L41" s="96"/>
       <c r="M41" s="38"/>
       <c r="N41" s="77"/>
@@ -3415,72 +3413,86 @@
     </row>
     <row r="43" spans="1:21" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A43" s="81"/>
-      <c r="B43" s="135" t="s">
+      <c r="B43" s="99" t="s">
         <v>11</v>
       </c>
-      <c r="C43" s="135"/>
-      <c r="D43" s="135"/>
-      <c r="E43" s="135"/>
-      <c r="F43" s="135"/>
-      <c r="G43" s="135"/>
-      <c r="H43" s="135"/>
-      <c r="I43" s="135"/>
-      <c r="J43" s="135"/>
-      <c r="K43" s="135"/>
-      <c r="L43" s="135"/>
-      <c r="M43" s="135"/>
-      <c r="N43" s="135"/>
-      <c r="O43" s="135"/>
-      <c r="P43" s="135"/>
-      <c r="Q43" s="135"/>
-      <c r="R43" s="135"/>
-      <c r="S43" s="135"/>
-      <c r="T43" s="135"/>
+      <c r="C43" s="99"/>
+      <c r="D43" s="99"/>
+      <c r="E43" s="99"/>
+      <c r="F43" s="99"/>
+      <c r="G43" s="99"/>
+      <c r="H43" s="99"/>
+      <c r="I43" s="99"/>
+      <c r="J43" s="99"/>
+      <c r="K43" s="99"/>
+      <c r="L43" s="99"/>
+      <c r="M43" s="99"/>
+      <c r="N43" s="99"/>
+      <c r="O43" s="99"/>
+      <c r="P43" s="99"/>
+      <c r="Q43" s="99"/>
+      <c r="R43" s="99"/>
+      <c r="S43" s="99"/>
+      <c r="T43" s="99"/>
       <c r="U43" s="28"/>
     </row>
     <row r="44" spans="1:21" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="38"/>
-      <c r="B44" s="105" t="s">
+      <c r="B44" s="100" t="s">
         <v>47</v>
       </c>
-      <c r="C44" s="105"/>
-      <c r="D44" s="105"/>
-      <c r="E44" s="105"/>
-      <c r="F44" s="105"/>
-      <c r="G44" s="105"/>
-      <c r="H44" s="105"/>
-      <c r="I44" s="105"/>
-      <c r="J44" s="105"/>
-      <c r="K44" s="105"/>
-      <c r="L44" s="105"/>
-      <c r="M44" s="105"/>
-      <c r="N44" s="105"/>
-      <c r="O44" s="105"/>
-      <c r="P44" s="105"/>
-      <c r="Q44" s="105"/>
-      <c r="R44" s="105"/>
-      <c r="S44" s="105"/>
-      <c r="T44" s="105"/>
+      <c r="C44" s="100"/>
+      <c r="D44" s="100"/>
+      <c r="E44" s="100"/>
+      <c r="F44" s="100"/>
+      <c r="G44" s="100"/>
+      <c r="H44" s="100"/>
+      <c r="I44" s="100"/>
+      <c r="J44" s="100"/>
+      <c r="K44" s="100"/>
+      <c r="L44" s="100"/>
+      <c r="M44" s="100"/>
+      <c r="N44" s="100"/>
+      <c r="O44" s="100"/>
+      <c r="P44" s="100"/>
+      <c r="Q44" s="100"/>
+      <c r="R44" s="100"/>
+      <c r="S44" s="100"/>
+      <c r="T44" s="100"/>
       <c r="U44" s="2"/>
     </row>
   </sheetData>
-  <mergeCells count="57">
-    <mergeCell ref="Q39:T39"/>
-    <mergeCell ref="B43:T43"/>
-    <mergeCell ref="B44:T44"/>
-    <mergeCell ref="I31:T31"/>
-    <mergeCell ref="N38:P38"/>
-    <mergeCell ref="Q38:T38"/>
-    <mergeCell ref="C33:I33"/>
-    <mergeCell ref="C34:I34"/>
-    <mergeCell ref="C35:I35"/>
-    <mergeCell ref="C27:K27"/>
-    <mergeCell ref="M27:O27"/>
-    <mergeCell ref="P27:R27"/>
-    <mergeCell ref="S27:T27"/>
-    <mergeCell ref="B29:H29"/>
-    <mergeCell ref="L29:R29"/>
-    <mergeCell ref="S29:T29"/>
+  <mergeCells count="58">
+    <mergeCell ref="H9:T9"/>
+    <mergeCell ref="H10:T10"/>
+    <mergeCell ref="H11:T11"/>
+    <mergeCell ref="H12:L12"/>
+    <mergeCell ref="H2:O2"/>
+    <mergeCell ref="P2:S2"/>
+    <mergeCell ref="H3:O3"/>
+    <mergeCell ref="P3:S3"/>
+    <mergeCell ref="H4:O4"/>
+    <mergeCell ref="H5:N5"/>
+    <mergeCell ref="H7:O7"/>
+    <mergeCell ref="H13:J13"/>
+    <mergeCell ref="K13:T13"/>
+    <mergeCell ref="H14:J14"/>
+    <mergeCell ref="K14:T14"/>
+    <mergeCell ref="C24:K24"/>
+    <mergeCell ref="M24:O24"/>
+    <mergeCell ref="P24:R24"/>
+    <mergeCell ref="S24:T24"/>
+    <mergeCell ref="E19:T19"/>
+    <mergeCell ref="J21:L21"/>
+    <mergeCell ref="H17:T17"/>
+    <mergeCell ref="C25:K25"/>
+    <mergeCell ref="M25:O25"/>
+    <mergeCell ref="P25:R25"/>
+    <mergeCell ref="S25:T25"/>
+    <mergeCell ref="C26:K26"/>
+    <mergeCell ref="M26:O26"/>
+    <mergeCell ref="P26:R26"/>
+    <mergeCell ref="S26:T26"/>
     <mergeCell ref="L30:R30"/>
     <mergeCell ref="S30:T30"/>
     <mergeCell ref="L28:R28"/>
@@ -3492,36 +3504,23 @@
     <mergeCell ref="N34:T34"/>
     <mergeCell ref="J35:M35"/>
     <mergeCell ref="N35:T35"/>
-    <mergeCell ref="C25:K25"/>
-    <mergeCell ref="M25:O25"/>
-    <mergeCell ref="P25:R25"/>
-    <mergeCell ref="S25:T25"/>
-    <mergeCell ref="C26:K26"/>
-    <mergeCell ref="M26:O26"/>
-    <mergeCell ref="P26:R26"/>
-    <mergeCell ref="S26:T26"/>
-    <mergeCell ref="H13:J13"/>
-    <mergeCell ref="K13:T13"/>
-    <mergeCell ref="H14:J14"/>
-    <mergeCell ref="K14:T14"/>
-    <mergeCell ref="C24:K24"/>
-    <mergeCell ref="M24:O24"/>
-    <mergeCell ref="P24:R24"/>
-    <mergeCell ref="S24:T24"/>
-    <mergeCell ref="E19:T19"/>
-    <mergeCell ref="J21:L21"/>
-    <mergeCell ref="H17:T17"/>
-    <mergeCell ref="H9:T9"/>
-    <mergeCell ref="H10:T10"/>
-    <mergeCell ref="H11:T11"/>
-    <mergeCell ref="H12:L12"/>
-    <mergeCell ref="H2:O2"/>
-    <mergeCell ref="P2:S2"/>
-    <mergeCell ref="H3:O3"/>
-    <mergeCell ref="P3:S3"/>
-    <mergeCell ref="H4:O4"/>
-    <mergeCell ref="H5:N5"/>
-    <mergeCell ref="H7:O7"/>
+    <mergeCell ref="C27:K27"/>
+    <mergeCell ref="M27:O27"/>
+    <mergeCell ref="P27:R27"/>
+    <mergeCell ref="S27:T27"/>
+    <mergeCell ref="B29:H29"/>
+    <mergeCell ref="L29:R29"/>
+    <mergeCell ref="S29:T29"/>
+    <mergeCell ref="Q39:T39"/>
+    <mergeCell ref="B43:T43"/>
+    <mergeCell ref="B44:T44"/>
+    <mergeCell ref="I31:T31"/>
+    <mergeCell ref="N38:P38"/>
+    <mergeCell ref="Q38:T38"/>
+    <mergeCell ref="C33:I33"/>
+    <mergeCell ref="C34:I34"/>
+    <mergeCell ref="C35:I35"/>
+    <mergeCell ref="H41:K41"/>
   </mergeCells>
   <pageMargins left="0.3" right="0.2" top="0.5" bottom="0" header="0.25" footer="0"/>
   <pageSetup paperSize="9" scale="96" orientation="portrait" r:id="rId1"/>

--- a/resources/report/60/95/ex_imp/TID_111_VAT_INVOICE_IMP.xlsx
+++ b/resources/report/60/95/ex_imp/TID_111_VAT_INVOICE_IMP.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lvthe\OneDrive\Máy tính\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lvthe\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E82D2212-20BA-458B-9B1F-006070F08A1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D11E826-1631-46DD-8AFB-192376AF4E99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1650" yWindow="2000" windowWidth="21600" windowHeight="11180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Invoice" sheetId="5" r:id="rId1"/>
@@ -1556,7 +1556,7 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyFont="0" applyBorder="0"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyFont="0"/>
   </cellStyleXfs>
-  <cellXfs count="144">
+  <cellXfs count="145">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1873,6 +1873,12 @@
     <xf numFmtId="0" fontId="29" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="49" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="26" fillId="18" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -1927,21 +1933,21 @@
     <xf numFmtId="0" fontId="8" fillId="18" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="18" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="27" fillId="18" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1969,11 +1975,8 @@
     <xf numFmtId="0" fontId="42" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="43">
@@ -2297,34 +2300,34 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U44"/>
-  <sheetFormatPr defaultColWidth="9.28515625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:U45"/>
+  <sheetFormatPr defaultColWidth="9.26953125" defaultRowHeight="13" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="1.7109375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="4.5703125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="9.7109375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="1.7109375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" style="1" customWidth="1"/>
-    <col min="6" max="6" width="3.7109375" style="1" customWidth="1"/>
-    <col min="7" max="7" width="1.7109375" style="1" customWidth="1"/>
-    <col min="8" max="8" width="3.7109375" style="1" customWidth="1"/>
-    <col min="9" max="9" width="6.7109375" style="1" customWidth="1"/>
-    <col min="10" max="10" width="9.7109375" style="1" customWidth="1"/>
-    <col min="11" max="11" width="1.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="8.7109375" style="1" customWidth="1"/>
-    <col min="13" max="13" width="7.7109375" style="1" customWidth="1"/>
-    <col min="14" max="14" width="4.28515625" style="1" customWidth="1"/>
-    <col min="15" max="15" width="0.7109375" style="1" customWidth="1"/>
-    <col min="16" max="16" width="5.7109375" style="1" customWidth="1"/>
-    <col min="17" max="17" width="4.7109375" style="1" customWidth="1"/>
-    <col min="18" max="18" width="0.7109375" style="1" customWidth="1"/>
-    <col min="19" max="19" width="5.7109375" style="1" customWidth="1"/>
-    <col min="20" max="20" width="14.7109375" style="1" customWidth="1"/>
-    <col min="21" max="21" width="1.7109375" style="1" customWidth="1"/>
-    <col min="22" max="16384" width="9.28515625" style="1"/>
+    <col min="1" max="1" width="1.7265625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="4.54296875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="9.7265625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="1.7265625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="4.7265625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="3.7265625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="1.7265625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="3.7265625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="6.7265625" style="1" customWidth="1"/>
+    <col min="10" max="10" width="9.7265625" style="1" customWidth="1"/>
+    <col min="11" max="11" width="1.7265625" style="1" customWidth="1"/>
+    <col min="12" max="12" width="8.7265625" style="1" customWidth="1"/>
+    <col min="13" max="13" width="7.7265625" style="1" customWidth="1"/>
+    <col min="14" max="14" width="4.26953125" style="1" customWidth="1"/>
+    <col min="15" max="15" width="0.7265625" style="1" customWidth="1"/>
+    <col min="16" max="16" width="5.7265625" style="1" customWidth="1"/>
+    <col min="17" max="17" width="4.7265625" style="1" customWidth="1"/>
+    <col min="18" max="18" width="0.7265625" style="1" customWidth="1"/>
+    <col min="19" max="19" width="5.7265625" style="1" customWidth="1"/>
+    <col min="20" max="20" width="14.7265625" style="1" customWidth="1"/>
+    <col min="21" max="21" width="1.7265625" style="1" customWidth="1"/>
+    <col min="22" max="16384" width="9.26953125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="4.9000000000000004" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:21" ht="4.9000000000000004" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="32"/>
       <c r="B1" s="32"/>
       <c r="C1" s="32"/>
@@ -2346,7 +2349,7 @@
       <c r="S1" s="32"/>
       <c r="T1" s="32"/>
     </row>
-    <row r="2" spans="1:21" ht="25.15" customHeight="1" collapsed="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:21" ht="25.15" customHeight="1" collapsed="1" x14ac:dyDescent="0.25">
       <c r="A2" s="33"/>
       <c r="B2" s="34"/>
       <c r="C2" s="35"/>
@@ -2354,26 +2357,26 @@
       <c r="E2" s="35"/>
       <c r="F2" s="35"/>
       <c r="G2" s="35"/>
-      <c r="H2" s="136" t="s">
+      <c r="H2" s="138" t="s">
         <v>13</v>
       </c>
-      <c r="I2" s="136"/>
-      <c r="J2" s="136"/>
-      <c r="K2" s="136"/>
-      <c r="L2" s="136"/>
-      <c r="M2" s="136"/>
-      <c r="N2" s="136"/>
-      <c r="O2" s="136"/>
-      <c r="P2" s="137" t="s">
+      <c r="I2" s="138"/>
+      <c r="J2" s="138"/>
+      <c r="K2" s="138"/>
+      <c r="L2" s="138"/>
+      <c r="M2" s="138"/>
+      <c r="N2" s="138"/>
+      <c r="O2" s="138"/>
+      <c r="P2" s="139" t="s">
         <v>42</v>
       </c>
-      <c r="Q2" s="137"/>
-      <c r="R2" s="137"/>
-      <c r="S2" s="137"/>
+      <c r="Q2" s="139"/>
+      <c r="R2" s="139"/>
+      <c r="S2" s="139"/>
       <c r="T2" s="36"/>
       <c r="U2" s="11"/>
     </row>
-    <row r="3" spans="1:21" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:21" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="37"/>
       <c r="B3" s="38"/>
       <c r="C3" s="38"/>
@@ -2381,26 +2384,26 @@
       <c r="E3" s="38"/>
       <c r="F3" s="38"/>
       <c r="G3" s="38"/>
-      <c r="H3" s="138" t="s">
+      <c r="H3" s="140" t="s">
         <v>33</v>
       </c>
-      <c r="I3" s="138"/>
-      <c r="J3" s="138"/>
-      <c r="K3" s="138"/>
-      <c r="L3" s="138"/>
-      <c r="M3" s="138"/>
-      <c r="N3" s="138"/>
-      <c r="O3" s="138"/>
-      <c r="P3" s="139" t="s">
+      <c r="I3" s="140"/>
+      <c r="J3" s="140"/>
+      <c r="K3" s="140"/>
+      <c r="L3" s="140"/>
+      <c r="M3" s="140"/>
+      <c r="N3" s="140"/>
+      <c r="O3" s="140"/>
+      <c r="P3" s="141" t="s">
         <v>43</v>
       </c>
-      <c r="Q3" s="139"/>
-      <c r="R3" s="139"/>
-      <c r="S3" s="139"/>
+      <c r="Q3" s="141"/>
+      <c r="R3" s="141"/>
+      <c r="S3" s="141"/>
       <c r="T3" s="39"/>
       <c r="U3" s="12"/>
     </row>
-    <row r="4" spans="1:21" ht="13.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:21" ht="13.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="37"/>
       <c r="B4" s="38"/>
       <c r="C4" s="38"/>
@@ -2423,32 +2426,30 @@
       <c r="T4" s="40"/>
       <c r="U4" s="12"/>
     </row>
-    <row r="5" spans="1:21" ht="15.4" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:21" ht="13.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="37"/>
-      <c r="B5" s="38"/>
-      <c r="C5" s="38"/>
-      <c r="D5" s="38"/>
-      <c r="E5" s="38"/>
-      <c r="F5" s="38"/>
-      <c r="G5" s="38"/>
-      <c r="H5" s="140" t="s">
-        <v>45</v>
-      </c>
-      <c r="I5" s="140"/>
-      <c r="J5" s="140"/>
-      <c r="K5" s="140"/>
-      <c r="L5" s="140"/>
-      <c r="M5" s="140"/>
-      <c r="N5" s="140"/>
-      <c r="O5" s="40"/>
-      <c r="P5" s="40"/>
-      <c r="Q5" s="40"/>
-      <c r="R5" s="40"/>
-      <c r="S5" s="40"/>
-      <c r="T5" s="40"/>
-      <c r="U5" s="13"/>
-    </row>
-    <row r="6" spans="1:21" ht="4.9000000000000004" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B5" s="144"/>
+      <c r="C5" s="144"/>
+      <c r="D5" s="144"/>
+      <c r="E5" s="144"/>
+      <c r="F5" s="144"/>
+      <c r="G5" s="144"/>
+      <c r="H5" s="144"/>
+      <c r="I5" s="144"/>
+      <c r="J5" s="144"/>
+      <c r="K5" s="144"/>
+      <c r="L5" s="144"/>
+      <c r="M5" s="144"/>
+      <c r="N5" s="144"/>
+      <c r="O5" s="144"/>
+      <c r="P5" s="144"/>
+      <c r="Q5" s="144"/>
+      <c r="R5" s="144"/>
+      <c r="S5" s="144"/>
+      <c r="T5" s="144"/>
+      <c r="U5" s="12"/>
+    </row>
+    <row r="6" spans="1:21" ht="15.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="37"/>
       <c r="B6" s="38"/>
       <c r="C6" s="38"/>
@@ -2456,13 +2457,15 @@
       <c r="E6" s="38"/>
       <c r="F6" s="38"/>
       <c r="G6" s="38"/>
-      <c r="H6" s="40"/>
-      <c r="I6" s="40"/>
-      <c r="J6" s="40"/>
-      <c r="K6" s="40"/>
-      <c r="L6" s="40"/>
-      <c r="M6" s="40"/>
-      <c r="N6" s="40"/>
+      <c r="H6" s="142" t="s">
+        <v>45</v>
+      </c>
+      <c r="I6" s="142"/>
+      <c r="J6" s="142"/>
+      <c r="K6" s="142"/>
+      <c r="L6" s="142"/>
+      <c r="M6" s="142"/>
+      <c r="N6" s="142"/>
       <c r="O6" s="40"/>
       <c r="P6" s="40"/>
       <c r="Q6" s="40"/>
@@ -2471,112 +2474,108 @@
       <c r="T6" s="40"/>
       <c r="U6" s="13"/>
     </row>
-    <row r="7" spans="1:21" ht="12" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:21" ht="4.9000000000000004" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="37"/>
       <c r="B7" s="38"/>
       <c r="C7" s="38"/>
       <c r="D7" s="38"/>
       <c r="E7" s="38"/>
-      <c r="F7" s="75" t="s">
+      <c r="F7" s="38"/>
+      <c r="G7" s="38"/>
+      <c r="H7" s="40"/>
+      <c r="I7" s="40"/>
+      <c r="J7" s="40"/>
+      <c r="K7" s="40"/>
+      <c r="L7" s="40"/>
+      <c r="M7" s="40"/>
+      <c r="N7" s="40"/>
+      <c r="O7" s="40"/>
+      <c r="P7" s="40"/>
+      <c r="Q7" s="40"/>
+      <c r="R7" s="40"/>
+      <c r="S7" s="40"/>
+      <c r="T7" s="40"/>
+      <c r="U7" s="13"/>
+    </row>
+    <row r="8" spans="1:21" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="37"/>
+      <c r="B8" s="38"/>
+      <c r="C8" s="38"/>
+      <c r="D8" s="38"/>
+      <c r="E8" s="38"/>
+      <c r="F8" s="75" t="s">
         <v>46</v>
       </c>
-      <c r="G7" s="75"/>
-      <c r="H7" s="141"/>
-      <c r="I7" s="141"/>
-      <c r="J7" s="141"/>
-      <c r="K7" s="141"/>
-      <c r="L7" s="141"/>
-      <c r="M7" s="141"/>
-      <c r="N7" s="141"/>
-      <c r="O7" s="141"/>
-      <c r="P7" s="94"/>
-      <c r="Q7" s="94"/>
-      <c r="R7" s="38"/>
-      <c r="S7" s="38"/>
-      <c r="T7" s="38"/>
-      <c r="U7" s="13"/>
-    </row>
-    <row r="8" spans="1:21" ht="3" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="37"/>
-      <c r="B8" s="41"/>
-      <c r="C8" s="41"/>
-      <c r="D8" s="41"/>
-      <c r="E8" s="41"/>
-      <c r="F8" s="41"/>
-      <c r="G8" s="41"/>
-      <c r="H8" s="42"/>
-      <c r="I8" s="42"/>
-      <c r="J8" s="42"/>
-      <c r="K8" s="38"/>
-      <c r="L8" s="38"/>
-      <c r="M8" s="38"/>
-      <c r="N8" s="38"/>
-      <c r="O8" s="38"/>
-      <c r="P8" s="38"/>
-      <c r="Q8" s="38"/>
+      <c r="G8" s="75"/>
+      <c r="H8" s="143"/>
+      <c r="I8" s="143"/>
+      <c r="J8" s="143"/>
+      <c r="K8" s="143"/>
+      <c r="L8" s="143"/>
+      <c r="M8" s="143"/>
+      <c r="N8" s="143"/>
+      <c r="O8" s="143"/>
+      <c r="P8" s="94"/>
+      <c r="Q8" s="94"/>
       <c r="R8" s="38"/>
       <c r="S8" s="38"/>
       <c r="T8" s="38"/>
-      <c r="U8" s="12"/>
-    </row>
-    <row r="9" spans="1:21" ht="25.15" customHeight="1" collapsed="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="43"/>
-      <c r="B9" s="44" t="s">
+      <c r="U8" s="13"/>
+    </row>
+    <row r="9" spans="1:21" ht="3" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="37"/>
+      <c r="B9" s="41"/>
+      <c r="C9" s="41"/>
+      <c r="D9" s="41"/>
+      <c r="E9" s="41"/>
+      <c r="F9" s="41"/>
+      <c r="G9" s="41"/>
+      <c r="H9" s="42"/>
+      <c r="I9" s="42"/>
+      <c r="J9" s="42"/>
+      <c r="K9" s="38"/>
+      <c r="L9" s="38"/>
+      <c r="M9" s="38"/>
+      <c r="N9" s="38"/>
+      <c r="O9" s="38"/>
+      <c r="P9" s="38"/>
+      <c r="Q9" s="38"/>
+      <c r="R9" s="38"/>
+      <c r="S9" s="38"/>
+      <c r="T9" s="38"/>
+      <c r="U9" s="12"/>
+    </row>
+    <row r="10" spans="1:21" ht="24.25" customHeight="1" collapsed="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="43"/>
+      <c r="B10" s="44" t="s">
         <v>26</v>
       </c>
-      <c r="C9" s="45"/>
-      <c r="D9" s="45"/>
-      <c r="E9" s="45"/>
-      <c r="F9" s="45"/>
-      <c r="G9" s="95" t="s">
+      <c r="C10" s="45"/>
+      <c r="D10" s="45"/>
+      <c r="E10" s="45"/>
+      <c r="F10" s="45"/>
+      <c r="G10" s="95" t="s">
         <v>16</v>
       </c>
-      <c r="H9" s="133"/>
-      <c r="I9" s="133"/>
-      <c r="J9" s="133"/>
-      <c r="K9" s="133"/>
-      <c r="L9" s="133"/>
-      <c r="M9" s="133"/>
-      <c r="N9" s="133"/>
-      <c r="O9" s="133"/>
-      <c r="P9" s="133"/>
-      <c r="Q9" s="133"/>
-      <c r="R9" s="133"/>
-      <c r="S9" s="133"/>
-      <c r="T9" s="133"/>
-      <c r="U9" s="14"/>
-    </row>
-    <row r="10" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="37"/>
-      <c r="B10" s="41" t="s">
-        <v>27</v>
-      </c>
-      <c r="C10" s="38"/>
-      <c r="D10" s="38"/>
-      <c r="E10" s="38"/>
-      <c r="F10" s="38"/>
-      <c r="G10" s="38" t="s">
-        <v>16</v>
-      </c>
-      <c r="H10" s="134"/>
-      <c r="I10" s="134"/>
-      <c r="J10" s="134"/>
-      <c r="K10" s="134"/>
-      <c r="L10" s="134"/>
-      <c r="M10" s="134"/>
-      <c r="N10" s="134"/>
-      <c r="O10" s="134"/>
-      <c r="P10" s="134"/>
-      <c r="Q10" s="134"/>
-      <c r="R10" s="134"/>
-      <c r="S10" s="134"/>
-      <c r="T10" s="134"/>
-      <c r="U10" s="12"/>
-    </row>
-    <row r="11" spans="1:21" ht="25.15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H10" s="135"/>
+      <c r="I10" s="135"/>
+      <c r="J10" s="135"/>
+      <c r="K10" s="135"/>
+      <c r="L10" s="135"/>
+      <c r="M10" s="135"/>
+      <c r="N10" s="135"/>
+      <c r="O10" s="135"/>
+      <c r="P10" s="135"/>
+      <c r="Q10" s="135"/>
+      <c r="R10" s="135"/>
+      <c r="S10" s="135"/>
+      <c r="T10" s="135"/>
+      <c r="U10" s="14"/>
+    </row>
+    <row r="11" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="37"/>
       <c r="B11" s="41" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C11" s="38"/>
       <c r="D11" s="38"/>
@@ -2585,25 +2584,25 @@
       <c r="G11" s="38" t="s">
         <v>16</v>
       </c>
-      <c r="H11" s="135"/>
-      <c r="I11" s="135"/>
-      <c r="J11" s="135"/>
-      <c r="K11" s="135"/>
-      <c r="L11" s="135"/>
-      <c r="M11" s="135"/>
-      <c r="N11" s="135"/>
-      <c r="O11" s="135"/>
-      <c r="P11" s="135"/>
-      <c r="Q11" s="135"/>
-      <c r="R11" s="135"/>
-      <c r="S11" s="135"/>
-      <c r="T11" s="135"/>
+      <c r="H11" s="136"/>
+      <c r="I11" s="136"/>
+      <c r="J11" s="136"/>
+      <c r="K11" s="136"/>
+      <c r="L11" s="136"/>
+      <c r="M11" s="136"/>
+      <c r="N11" s="136"/>
+      <c r="O11" s="136"/>
+      <c r="P11" s="136"/>
+      <c r="Q11" s="136"/>
+      <c r="R11" s="136"/>
+      <c r="S11" s="136"/>
+      <c r="T11" s="136"/>
       <c r="U11" s="12"/>
     </row>
-    <row r="12" spans="1:21" ht="15.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:21" ht="25.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="37"/>
-      <c r="B12" s="46" t="s">
-        <v>29</v>
+      <c r="B12" s="41" t="s">
+        <v>28</v>
       </c>
       <c r="C12" s="38"/>
       <c r="D12" s="38"/>
@@ -2612,25 +2611,25 @@
       <c r="G12" s="38" t="s">
         <v>16</v>
       </c>
-      <c r="H12" s="128"/>
-      <c r="I12" s="128"/>
-      <c r="J12" s="128"/>
-      <c r="K12" s="128"/>
-      <c r="L12" s="128"/>
-      <c r="M12" s="42"/>
-      <c r="N12" s="42"/>
-      <c r="O12" s="42"/>
-      <c r="P12" s="42"/>
-      <c r="Q12" s="41"/>
-      <c r="R12" s="42"/>
-      <c r="S12" s="42"/>
-      <c r="T12" s="42"/>
-      <c r="U12" s="13"/>
-    </row>
-    <row r="13" spans="1:21" ht="15.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H12" s="137"/>
+      <c r="I12" s="137"/>
+      <c r="J12" s="137"/>
+      <c r="K12" s="137"/>
+      <c r="L12" s="137"/>
+      <c r="M12" s="137"/>
+      <c r="N12" s="137"/>
+      <c r="O12" s="137"/>
+      <c r="P12" s="137"/>
+      <c r="Q12" s="137"/>
+      <c r="R12" s="137"/>
+      <c r="S12" s="137"/>
+      <c r="T12" s="137"/>
+      <c r="U12" s="12"/>
+    </row>
+    <row r="13" spans="1:21" ht="15.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="37"/>
       <c r="B13" s="46" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C13" s="38"/>
       <c r="D13" s="38"/>
@@ -2639,221 +2638,223 @@
       <c r="G13" s="38" t="s">
         <v>16</v>
       </c>
-      <c r="H13" s="128"/>
-      <c r="I13" s="128"/>
-      <c r="J13" s="128"/>
-      <c r="K13" s="128"/>
-      <c r="L13" s="128"/>
-      <c r="M13" s="128"/>
-      <c r="N13" s="128"/>
-      <c r="O13" s="128"/>
-      <c r="P13" s="128"/>
-      <c r="Q13" s="128"/>
-      <c r="R13" s="128"/>
-      <c r="S13" s="128"/>
-      <c r="T13" s="128"/>
+      <c r="H13" s="131"/>
+      <c r="I13" s="131"/>
+      <c r="J13" s="131"/>
+      <c r="K13" s="131"/>
+      <c r="L13" s="131"/>
+      <c r="M13" s="42"/>
+      <c r="N13" s="42"/>
+      <c r="O13" s="42"/>
+      <c r="P13" s="42"/>
+      <c r="Q13" s="41"/>
+      <c r="R13" s="42"/>
+      <c r="S13" s="42"/>
+      <c r="T13" s="42"/>
       <c r="U13" s="13"/>
     </row>
-    <row r="14" spans="1:21" ht="13.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:21" ht="15.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="37"/>
-      <c r="B14" s="38"/>
+      <c r="B14" s="46" t="s">
+        <v>30</v>
+      </c>
       <c r="C14" s="38"/>
       <c r="D14" s="38"/>
       <c r="E14" s="38"/>
       <c r="F14" s="38"/>
-      <c r="G14" s="38"/>
-      <c r="H14" s="129"/>
-      <c r="I14" s="129"/>
-      <c r="J14" s="129"/>
-      <c r="K14" s="129"/>
-      <c r="L14" s="129"/>
-      <c r="M14" s="129"/>
-      <c r="N14" s="129"/>
-      <c r="O14" s="129"/>
-      <c r="P14" s="129"/>
-      <c r="Q14" s="129"/>
-      <c r="R14" s="129"/>
-      <c r="S14" s="129"/>
-      <c r="T14" s="129"/>
+      <c r="G14" s="38" t="s">
+        <v>16</v>
+      </c>
+      <c r="H14" s="131"/>
+      <c r="I14" s="131"/>
+      <c r="J14" s="131"/>
+      <c r="K14" s="131"/>
+      <c r="L14" s="131"/>
+      <c r="M14" s="131"/>
+      <c r="N14" s="131"/>
+      <c r="O14" s="131"/>
+      <c r="P14" s="131"/>
+      <c r="Q14" s="131"/>
+      <c r="R14" s="131"/>
+      <c r="S14" s="131"/>
+      <c r="T14" s="131"/>
       <c r="U14" s="13"/>
     </row>
-    <row r="15" spans="1:21" ht="4.9000000000000004" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:21" ht="13.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="37"/>
-      <c r="B15" s="47"/>
-      <c r="C15" s="47"/>
-      <c r="D15" s="47"/>
-      <c r="E15" s="47"/>
-      <c r="F15" s="47"/>
-      <c r="G15" s="47"/>
-      <c r="H15" s="44"/>
-      <c r="I15" s="44"/>
-      <c r="J15" s="48"/>
-      <c r="K15" s="48"/>
-      <c r="L15" s="88"/>
-      <c r="M15" s="88"/>
-      <c r="N15" s="88"/>
-      <c r="O15" s="88"/>
-      <c r="P15" s="88"/>
-      <c r="Q15" s="88"/>
-      <c r="R15" s="88"/>
-      <c r="S15" s="88"/>
-      <c r="T15" s="88"/>
+      <c r="B15" s="38"/>
+      <c r="C15" s="38"/>
+      <c r="D15" s="38"/>
+      <c r="E15" s="38"/>
+      <c r="F15" s="38"/>
+      <c r="G15" s="38"/>
+      <c r="H15" s="134"/>
+      <c r="I15" s="134"/>
+      <c r="J15" s="134"/>
+      <c r="K15" s="134"/>
+      <c r="L15" s="134"/>
+      <c r="M15" s="134"/>
+      <c r="N15" s="134"/>
+      <c r="O15" s="134"/>
+      <c r="P15" s="134"/>
+      <c r="Q15" s="134"/>
+      <c r="R15" s="134"/>
+      <c r="S15" s="134"/>
+      <c r="T15" s="134"/>
       <c r="U15" s="13"/>
     </row>
-    <row r="16" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:21" ht="4.9000000000000004" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="37"/>
-      <c r="B16" s="41" t="s">
-        <v>32</v>
-      </c>
-      <c r="C16" s="41"/>
-      <c r="D16" s="41"/>
-      <c r="E16" s="41"/>
-      <c r="F16" s="41"/>
-      <c r="G16" s="41"/>
-      <c r="H16" s="49"/>
-      <c r="I16" s="49"/>
-      <c r="J16" s="49"/>
-      <c r="K16" s="50"/>
-      <c r="L16" s="50"/>
-      <c r="M16" s="50"/>
-      <c r="N16" s="50"/>
-      <c r="O16" s="50"/>
-      <c r="P16" s="50"/>
-      <c r="Q16" s="50"/>
-      <c r="R16" s="50"/>
-      <c r="S16" s="50"/>
-      <c r="T16" s="50"/>
-      <c r="U16" s="29"/>
-    </row>
-    <row r="17" spans="1:21" ht="22.15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B16" s="47"/>
+      <c r="C16" s="47"/>
+      <c r="D16" s="47"/>
+      <c r="E16" s="47"/>
+      <c r="F16" s="47"/>
+      <c r="G16" s="47"/>
+      <c r="H16" s="44"/>
+      <c r="I16" s="44"/>
+      <c r="J16" s="48"/>
+      <c r="K16" s="48"/>
+      <c r="L16" s="88"/>
+      <c r="M16" s="88"/>
+      <c r="N16" s="88"/>
+      <c r="O16" s="88"/>
+      <c r="P16" s="88"/>
+      <c r="Q16" s="88"/>
+      <c r="R16" s="88"/>
+      <c r="S16" s="88"/>
+      <c r="T16" s="88"/>
+      <c r="U16" s="13"/>
+    </row>
+    <row r="17" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="37"/>
       <c r="B17" s="41" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="C17" s="41"/>
       <c r="D17" s="41"/>
       <c r="E17" s="41"/>
       <c r="F17" s="41"/>
       <c r="G17" s="41"/>
-      <c r="H17" s="132"/>
-      <c r="I17" s="132"/>
-      <c r="J17" s="132"/>
-      <c r="K17" s="132"/>
-      <c r="L17" s="132"/>
-      <c r="M17" s="132"/>
-      <c r="N17" s="132"/>
-      <c r="O17" s="132"/>
-      <c r="P17" s="132"/>
-      <c r="Q17" s="132"/>
-      <c r="R17" s="132"/>
-      <c r="S17" s="132"/>
-      <c r="T17" s="132"/>
-      <c r="U17" s="15"/>
-    </row>
-    <row r="18" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H17" s="49"/>
+      <c r="I17" s="49"/>
+      <c r="J17" s="49"/>
+      <c r="K17" s="50"/>
+      <c r="L17" s="50"/>
+      <c r="M17" s="50"/>
+      <c r="N17" s="50"/>
+      <c r="O17" s="50"/>
+      <c r="P17" s="50"/>
+      <c r="Q17" s="50"/>
+      <c r="R17" s="50"/>
+      <c r="S17" s="50"/>
+      <c r="T17" s="50"/>
+      <c r="U17" s="29"/>
+    </row>
+    <row r="18" spans="1:21" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="37"/>
       <c r="B18" s="41" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="C18" s="41"/>
       <c r="D18" s="41"/>
       <c r="E18" s="41"/>
       <c r="F18" s="41"/>
       <c r="G18" s="41"/>
-      <c r="H18" s="49"/>
-      <c r="I18" s="49"/>
-      <c r="J18" s="51"/>
-      <c r="K18" s="51"/>
-      <c r="L18" s="51"/>
-      <c r="M18" s="41"/>
-      <c r="N18" s="51"/>
-      <c r="O18" s="51"/>
-      <c r="P18" s="51"/>
-      <c r="Q18" s="51"/>
-      <c r="R18" s="51"/>
-      <c r="S18" s="51"/>
-      <c r="T18" s="51"/>
+      <c r="H18" s="133"/>
+      <c r="I18" s="133"/>
+      <c r="J18" s="133"/>
+      <c r="K18" s="133"/>
+      <c r="L18" s="133"/>
+      <c r="M18" s="133"/>
+      <c r="N18" s="133"/>
+      <c r="O18" s="133"/>
+      <c r="P18" s="133"/>
+      <c r="Q18" s="133"/>
+      <c r="R18" s="133"/>
+      <c r="S18" s="133"/>
+      <c r="T18" s="133"/>
       <c r="U18" s="15"/>
     </row>
-    <row r="19" spans="1:21" ht="25.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="37"/>
       <c r="B19" s="41" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C19" s="41"/>
       <c r="D19" s="41"/>
-      <c r="E19" s="128"/>
-      <c r="F19" s="128"/>
-      <c r="G19" s="128"/>
-      <c r="H19" s="128"/>
-      <c r="I19" s="128"/>
-      <c r="J19" s="128"/>
-      <c r="K19" s="128"/>
-      <c r="L19" s="128"/>
-      <c r="M19" s="128"/>
-      <c r="N19" s="128"/>
-      <c r="O19" s="128"/>
-      <c r="P19" s="128"/>
-      <c r="Q19" s="128"/>
-      <c r="R19" s="128"/>
-      <c r="S19" s="128"/>
-      <c r="T19" s="128"/>
+      <c r="E19" s="41"/>
+      <c r="F19" s="41"/>
+      <c r="G19" s="41"/>
+      <c r="H19" s="49"/>
+      <c r="I19" s="49"/>
+      <c r="J19" s="51"/>
+      <c r="K19" s="51"/>
+      <c r="L19" s="51"/>
+      <c r="M19" s="41"/>
+      <c r="N19" s="51"/>
+      <c r="O19" s="51"/>
+      <c r="P19" s="51"/>
+      <c r="Q19" s="51"/>
+      <c r="R19" s="51"/>
+      <c r="S19" s="51"/>
+      <c r="T19" s="51"/>
       <c r="U19" s="15"/>
     </row>
-    <row r="20" spans="1:21" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:21" ht="25.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="37"/>
       <c r="B20" s="41" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="C20" s="41"/>
       <c r="D20" s="41"/>
-      <c r="E20" s="41"/>
-      <c r="F20" s="41"/>
-      <c r="G20" s="41"/>
-      <c r="H20" s="49"/>
-      <c r="I20" s="49"/>
-      <c r="J20" s="51"/>
-      <c r="K20" s="51"/>
-      <c r="L20" s="51"/>
-      <c r="M20" s="41"/>
-      <c r="N20" s="51"/>
-      <c r="O20" s="51"/>
-      <c r="P20" s="51"/>
-      <c r="Q20" s="51"/>
-      <c r="R20" s="51"/>
-      <c r="S20" s="51"/>
-      <c r="T20" s="51"/>
+      <c r="E20" s="131"/>
+      <c r="F20" s="131"/>
+      <c r="G20" s="131"/>
+      <c r="H20" s="131"/>
+      <c r="I20" s="131"/>
+      <c r="J20" s="131"/>
+      <c r="K20" s="131"/>
+      <c r="L20" s="131"/>
+      <c r="M20" s="131"/>
+      <c r="N20" s="131"/>
+      <c r="O20" s="131"/>
+      <c r="P20" s="131"/>
+      <c r="Q20" s="131"/>
+      <c r="R20" s="131"/>
+      <c r="S20" s="131"/>
+      <c r="T20" s="131"/>
       <c r="U20" s="15"/>
     </row>
-    <row r="21" spans="1:21" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:21" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="37"/>
       <c r="B21" s="41" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C21" s="41"/>
       <c r="D21" s="41"/>
       <c r="E21" s="41"/>
       <c r="F21" s="41"/>
       <c r="G21" s="41"/>
-      <c r="H21" s="38"/>
-      <c r="I21" s="38"/>
-      <c r="J21" s="131"/>
-      <c r="K21" s="131"/>
-      <c r="L21" s="131"/>
-      <c r="M21" s="38"/>
-      <c r="N21" s="38"/>
-      <c r="O21" s="38"/>
-      <c r="P21" s="38"/>
-      <c r="Q21" s="38"/>
-      <c r="R21" s="38"/>
-      <c r="S21" s="38"/>
-      <c r="T21" s="38"/>
-      <c r="U21" s="12"/>
-    </row>
-    <row r="22" spans="1:21" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="H21" s="49"/>
+      <c r="I21" s="49"/>
+      <c r="J21" s="51"/>
+      <c r="K21" s="51"/>
+      <c r="L21" s="51"/>
+      <c r="M21" s="41"/>
+      <c r="N21" s="51"/>
+      <c r="O21" s="51"/>
+      <c r="P21" s="51"/>
+      <c r="Q21" s="51"/>
+      <c r="R21" s="51"/>
+      <c r="S21" s="51"/>
+      <c r="T21" s="51"/>
+      <c r="U21" s="15"/>
+    </row>
+    <row r="22" spans="1:21" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="37"/>
       <c r="B22" s="41" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C22" s="41"/>
       <c r="D22" s="41"/>
@@ -2862,12 +2863,10 @@
       <c r="G22" s="41"/>
       <c r="H22" s="38"/>
       <c r="I22" s="38"/>
-      <c r="J22" s="38"/>
-      <c r="K22" s="52"/>
-      <c r="L22" s="41"/>
-      <c r="M22" s="38" t="s">
-        <v>21</v>
-      </c>
+      <c r="J22" s="132"/>
+      <c r="K22" s="132"/>
+      <c r="L22" s="132"/>
+      <c r="M22" s="38"/>
       <c r="N22" s="38"/>
       <c r="O22" s="38"/>
       <c r="P22" s="38"/>
@@ -2877,9 +2876,11 @@
       <c r="T22" s="38"/>
       <c r="U22" s="12"/>
     </row>
-    <row r="23" spans="1:21" ht="3" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:21" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="37"/>
-      <c r="B23" s="41"/>
+      <c r="B23" s="41" t="s">
+        <v>22</v>
+      </c>
       <c r="C23" s="41"/>
       <c r="D23" s="41"/>
       <c r="E23" s="41"/>
@@ -2890,7 +2891,9 @@
       <c r="J23" s="38"/>
       <c r="K23" s="52"/>
       <c r="L23" s="41"/>
-      <c r="M23" s="38"/>
+      <c r="M23" s="38" t="s">
+        <v>21</v>
+      </c>
       <c r="N23" s="38"/>
       <c r="O23" s="38"/>
       <c r="P23" s="38"/>
@@ -2900,482 +2903,478 @@
       <c r="T23" s="38"/>
       <c r="U23" s="12"/>
     </row>
-    <row r="24" spans="1:21" s="3" customFormat="1" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A24" s="53"/>
-      <c r="B24" s="54" t="s">
+    <row r="24" spans="1:21" ht="3" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="37"/>
+      <c r="B24" s="41"/>
+      <c r="C24" s="41"/>
+      <c r="D24" s="41"/>
+      <c r="E24" s="41"/>
+      <c r="F24" s="41"/>
+      <c r="G24" s="41"/>
+      <c r="H24" s="38"/>
+      <c r="I24" s="38"/>
+      <c r="J24" s="38"/>
+      <c r="K24" s="52"/>
+      <c r="L24" s="41"/>
+      <c r="M24" s="38"/>
+      <c r="N24" s="38"/>
+      <c r="O24" s="38"/>
+      <c r="P24" s="38"/>
+      <c r="Q24" s="38"/>
+      <c r="R24" s="38"/>
+      <c r="S24" s="38"/>
+      <c r="T24" s="38"/>
+      <c r="U24" s="12"/>
+    </row>
+    <row r="25" spans="1:21" s="3" customFormat="1" ht="15.5" x14ac:dyDescent="0.25">
+      <c r="A25" s="53"/>
+      <c r="B25" s="54" t="s">
         <v>0</v>
       </c>
-      <c r="C24" s="130" t="s">
+      <c r="C25" s="130" t="s">
         <v>2</v>
       </c>
-      <c r="D24" s="130"/>
-      <c r="E24" s="130"/>
-      <c r="F24" s="130"/>
-      <c r="G24" s="130"/>
-      <c r="H24" s="130"/>
-      <c r="I24" s="130"/>
-      <c r="J24" s="130"/>
-      <c r="K24" s="130"/>
-      <c r="L24" s="83" t="s">
+      <c r="D25" s="130"/>
+      <c r="E25" s="130"/>
+      <c r="F25" s="130"/>
+      <c r="G25" s="130"/>
+      <c r="H25" s="130"/>
+      <c r="I25" s="130"/>
+      <c r="J25" s="130"/>
+      <c r="K25" s="130"/>
+      <c r="L25" s="83" t="s">
         <v>31</v>
       </c>
-      <c r="M24" s="130" t="s">
+      <c r="M25" s="130" t="s">
         <v>4</v>
       </c>
-      <c r="N24" s="130"/>
-      <c r="O24" s="130"/>
-      <c r="P24" s="130" t="s">
+      <c r="N25" s="130"/>
+      <c r="O25" s="130"/>
+      <c r="P25" s="130" t="s">
         <v>5</v>
       </c>
-      <c r="Q24" s="130"/>
-      <c r="R24" s="130"/>
-      <c r="S24" s="130" t="s">
+      <c r="Q25" s="130"/>
+      <c r="R25" s="130"/>
+      <c r="S25" s="130" t="s">
         <v>7</v>
       </c>
-      <c r="T24" s="130"/>
-      <c r="U24" s="16"/>
-    </row>
-    <row r="25" spans="1:21" s="4" customFormat="1" ht="13.15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="55"/>
-      <c r="B25" s="84" t="s">
+      <c r="T25" s="130"/>
+      <c r="U25" s="16"/>
+    </row>
+    <row r="26" spans="1:21" s="4" customFormat="1" ht="13.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="55"/>
+      <c r="B26" s="84" t="s">
         <v>1</v>
       </c>
-      <c r="C25" s="126" t="s">
+      <c r="C26" s="128" t="s">
         <v>17</v>
       </c>
-      <c r="D25" s="126"/>
-      <c r="E25" s="126"/>
-      <c r="F25" s="126"/>
-      <c r="G25" s="126"/>
-      <c r="H25" s="126"/>
-      <c r="I25" s="126"/>
-      <c r="J25" s="126"/>
-      <c r="K25" s="126"/>
-      <c r="L25" s="84" t="s">
+      <c r="D26" s="128"/>
+      <c r="E26" s="128"/>
+      <c r="F26" s="128"/>
+      <c r="G26" s="128"/>
+      <c r="H26" s="128"/>
+      <c r="I26" s="128"/>
+      <c r="J26" s="128"/>
+      <c r="K26" s="128"/>
+      <c r="L26" s="84" t="s">
         <v>3</v>
       </c>
-      <c r="M25" s="126" t="s">
+      <c r="M26" s="128" t="s">
         <v>14</v>
       </c>
-      <c r="N25" s="126"/>
-      <c r="O25" s="126"/>
-      <c r="P25" s="126" t="s">
+      <c r="N26" s="128"/>
+      <c r="O26" s="128"/>
+      <c r="P26" s="128" t="s">
         <v>6</v>
       </c>
-      <c r="Q25" s="126"/>
-      <c r="R25" s="126"/>
-      <c r="S25" s="126" t="s">
+      <c r="Q26" s="128"/>
+      <c r="R26" s="128"/>
+      <c r="S26" s="128" t="s">
         <v>8</v>
       </c>
-      <c r="T25" s="126"/>
-      <c r="U25" s="17"/>
-    </row>
-    <row r="26" spans="1:21" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="56"/>
-      <c r="B26" s="85">
+      <c r="T26" s="128"/>
+      <c r="U26" s="17"/>
+    </row>
+    <row r="27" spans="1:21" s="5" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="56"/>
+      <c r="B27" s="85">
         <v>1</v>
       </c>
-      <c r="C26" s="127">
+      <c r="C27" s="129">
         <v>2</v>
       </c>
-      <c r="D26" s="127"/>
-      <c r="E26" s="127"/>
-      <c r="F26" s="127"/>
-      <c r="G26" s="127"/>
-      <c r="H26" s="127"/>
-      <c r="I26" s="127"/>
-      <c r="J26" s="127"/>
-      <c r="K26" s="127"/>
-      <c r="L26" s="85">
+      <c r="D27" s="129"/>
+      <c r="E27" s="129"/>
+      <c r="F27" s="129"/>
+      <c r="G27" s="129"/>
+      <c r="H27" s="129"/>
+      <c r="I27" s="129"/>
+      <c r="J27" s="129"/>
+      <c r="K27" s="129"/>
+      <c r="L27" s="85">
         <v>3</v>
       </c>
-      <c r="M26" s="127">
+      <c r="M27" s="129">
         <v>4</v>
       </c>
-      <c r="N26" s="127"/>
-      <c r="O26" s="127"/>
-      <c r="P26" s="127">
+      <c r="N27" s="129"/>
+      <c r="O27" s="129"/>
+      <c r="P27" s="129">
         <v>5</v>
       </c>
-      <c r="Q26" s="127"/>
-      <c r="R26" s="127"/>
-      <c r="S26" s="127" t="s">
+      <c r="Q27" s="129"/>
+      <c r="R27" s="129"/>
+      <c r="S27" s="129" t="s">
         <v>18</v>
       </c>
-      <c r="T26" s="127"/>
-      <c r="U26" s="18"/>
-    </row>
-    <row r="27" spans="1:21" s="3" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="57"/>
-      <c r="B27" s="89"/>
-      <c r="C27" s="110"/>
-      <c r="D27" s="111"/>
-      <c r="E27" s="111"/>
-      <c r="F27" s="111"/>
-      <c r="G27" s="111"/>
-      <c r="H27" s="111"/>
-      <c r="I27" s="111"/>
-      <c r="J27" s="111"/>
-      <c r="K27" s="112"/>
-      <c r="L27" s="90"/>
-      <c r="M27" s="113"/>
-      <c r="N27" s="114"/>
-      <c r="O27" s="115"/>
-      <c r="P27" s="113"/>
-      <c r="Q27" s="114"/>
-      <c r="R27" s="115"/>
-      <c r="S27" s="116"/>
-      <c r="T27" s="117"/>
-      <c r="U27" s="30"/>
-    </row>
-    <row r="28" spans="1:21" s="6" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="T27" s="129"/>
+      <c r="U27" s="18"/>
+    </row>
+    <row r="28" spans="1:21" s="3" customFormat="1" ht="17" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="57"/>
-      <c r="B28" s="58"/>
-      <c r="C28" s="59"/>
-      <c r="D28" s="60"/>
-      <c r="E28" s="60"/>
-      <c r="F28" s="60"/>
-      <c r="G28" s="60"/>
-      <c r="H28" s="60"/>
-      <c r="I28" s="60"/>
-      <c r="J28" s="60"/>
-      <c r="K28" s="60"/>
-      <c r="L28" s="120" t="s">
+      <c r="B28" s="89"/>
+      <c r="C28" s="112"/>
+      <c r="D28" s="113"/>
+      <c r="E28" s="113"/>
+      <c r="F28" s="113"/>
+      <c r="G28" s="113"/>
+      <c r="H28" s="113"/>
+      <c r="I28" s="113"/>
+      <c r="J28" s="113"/>
+      <c r="K28" s="114"/>
+      <c r="L28" s="90"/>
+      <c r="M28" s="115"/>
+      <c r="N28" s="116"/>
+      <c r="O28" s="117"/>
+      <c r="P28" s="115"/>
+      <c r="Q28" s="116"/>
+      <c r="R28" s="117"/>
+      <c r="S28" s="118"/>
+      <c r="T28" s="119"/>
+      <c r="U28" s="30"/>
+    </row>
+    <row r="29" spans="1:21" s="6" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="57"/>
+      <c r="B29" s="58"/>
+      <c r="C29" s="59"/>
+      <c r="D29" s="60"/>
+      <c r="E29" s="60"/>
+      <c r="F29" s="60"/>
+      <c r="G29" s="60"/>
+      <c r="H29" s="60"/>
+      <c r="I29" s="60"/>
+      <c r="J29" s="60"/>
+      <c r="K29" s="60"/>
+      <c r="L29" s="122" t="s">
         <v>38</v>
       </c>
-      <c r="M28" s="120"/>
-      <c r="N28" s="120"/>
-      <c r="O28" s="120"/>
-      <c r="P28" s="120"/>
-      <c r="Q28" s="120"/>
-      <c r="R28" s="121"/>
-      <c r="S28" s="122"/>
-      <c r="T28" s="123"/>
-      <c r="U28" s="31"/>
-    </row>
-    <row r="29" spans="1:21" s="6" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="57"/>
-      <c r="B29" s="118" t="s">
+      <c r="M29" s="122"/>
+      <c r="N29" s="122"/>
+      <c r="O29" s="122"/>
+      <c r="P29" s="122"/>
+      <c r="Q29" s="122"/>
+      <c r="R29" s="123"/>
+      <c r="S29" s="124"/>
+      <c r="T29" s="125"/>
+      <c r="U29" s="31"/>
+    </row>
+    <row r="30" spans="1:21" s="6" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="57"/>
+      <c r="B30" s="120" t="s">
         <v>20</v>
       </c>
-      <c r="C29" s="119"/>
-      <c r="D29" s="119"/>
-      <c r="E29" s="119"/>
-      <c r="F29" s="119"/>
-      <c r="G29" s="119"/>
-      <c r="H29" s="119"/>
-      <c r="I29" s="87"/>
-      <c r="J29" s="61"/>
-      <c r="K29" s="87"/>
-      <c r="L29" s="120" t="s">
+      <c r="C30" s="121"/>
+      <c r="D30" s="121"/>
+      <c r="E30" s="121"/>
+      <c r="F30" s="121"/>
+      <c r="G30" s="121"/>
+      <c r="H30" s="121"/>
+      <c r="I30" s="87"/>
+      <c r="J30" s="61"/>
+      <c r="K30" s="87"/>
+      <c r="L30" s="122" t="s">
         <v>39</v>
       </c>
-      <c r="M29" s="120"/>
-      <c r="N29" s="120"/>
-      <c r="O29" s="120"/>
-      <c r="P29" s="120"/>
-      <c r="Q29" s="120"/>
-      <c r="R29" s="121"/>
-      <c r="S29" s="122"/>
-      <c r="T29" s="123"/>
-      <c r="U29" s="31"/>
-    </row>
-    <row r="30" spans="1:21" s="6" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="57"/>
-      <c r="B30" s="86"/>
-      <c r="C30" s="87"/>
-      <c r="D30" s="87"/>
-      <c r="E30" s="87"/>
-      <c r="F30" s="87"/>
-      <c r="G30" s="87"/>
-      <c r="H30" s="87"/>
-      <c r="I30" s="87"/>
-      <c r="J30" s="87"/>
-      <c r="K30" s="87"/>
-      <c r="L30" s="120" t="s">
+      <c r="M30" s="122"/>
+      <c r="N30" s="122"/>
+      <c r="O30" s="122"/>
+      <c r="P30" s="122"/>
+      <c r="Q30" s="122"/>
+      <c r="R30" s="123"/>
+      <c r="S30" s="124"/>
+      <c r="T30" s="125"/>
+      <c r="U30" s="31"/>
+    </row>
+    <row r="31" spans="1:21" s="6" customFormat="1" ht="19.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="57"/>
+      <c r="B31" s="86"/>
+      <c r="C31" s="87"/>
+      <c r="D31" s="87"/>
+      <c r="E31" s="87"/>
+      <c r="F31" s="87"/>
+      <c r="G31" s="87"/>
+      <c r="H31" s="87"/>
+      <c r="I31" s="87"/>
+      <c r="J31" s="87"/>
+      <c r="K31" s="87"/>
+      <c r="L31" s="122" t="s">
         <v>40</v>
       </c>
-      <c r="M30" s="120"/>
-      <c r="N30" s="120"/>
-      <c r="O30" s="120"/>
-      <c r="P30" s="120"/>
-      <c r="Q30" s="120"/>
-      <c r="R30" s="121"/>
-      <c r="S30" s="122"/>
-      <c r="T30" s="123"/>
-      <c r="U30" s="31"/>
-    </row>
-    <row r="31" spans="1:21" s="6" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="53"/>
-      <c r="B31" s="82" t="s">
+      <c r="M31" s="122"/>
+      <c r="N31" s="122"/>
+      <c r="O31" s="122"/>
+      <c r="P31" s="122"/>
+      <c r="Q31" s="122"/>
+      <c r="R31" s="123"/>
+      <c r="S31" s="124"/>
+      <c r="T31" s="125"/>
+      <c r="U31" s="31"/>
+    </row>
+    <row r="32" spans="1:21" s="6" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="53"/>
+      <c r="B32" s="82" t="s">
         <v>44</v>
       </c>
-      <c r="C31" s="44"/>
-      <c r="D31" s="44"/>
-      <c r="E31" s="44"/>
-      <c r="F31" s="44"/>
-      <c r="G31" s="44"/>
-      <c r="H31" s="44"/>
-      <c r="I31" s="101"/>
-      <c r="J31" s="101"/>
-      <c r="K31" s="101"/>
-      <c r="L31" s="101"/>
-      <c r="M31" s="101"/>
-      <c r="N31" s="101"/>
-      <c r="O31" s="101"/>
-      <c r="P31" s="101"/>
-      <c r="Q31" s="101"/>
-      <c r="R31" s="101"/>
-      <c r="S31" s="101"/>
-      <c r="T31" s="102"/>
-      <c r="U31" s="19"/>
-    </row>
-    <row r="32" spans="1:21" ht="4.9000000000000004" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="37"/>
-      <c r="B32" s="62"/>
-      <c r="C32" s="63"/>
-      <c r="D32" s="63"/>
-      <c r="E32" s="63"/>
-      <c r="F32" s="63"/>
-      <c r="G32" s="63"/>
-      <c r="H32" s="64"/>
-      <c r="I32" s="64"/>
-      <c r="J32" s="64"/>
-      <c r="K32" s="64"/>
-      <c r="L32" s="64"/>
-      <c r="M32" s="64"/>
-      <c r="N32" s="64"/>
-      <c r="O32" s="64"/>
-      <c r="P32" s="64"/>
-      <c r="Q32" s="64"/>
-      <c r="R32" s="64"/>
-      <c r="S32" s="64"/>
-      <c r="T32" s="65"/>
-      <c r="U32" s="20"/>
-    </row>
-    <row r="33" spans="1:21" s="7" customFormat="1" ht="15.4" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="66"/>
-      <c r="B33" s="67"/>
-      <c r="C33" s="107" t="s">
+      <c r="C32" s="44"/>
+      <c r="D32" s="44"/>
+      <c r="E32" s="44"/>
+      <c r="F32" s="44"/>
+      <c r="G32" s="44"/>
+      <c r="H32" s="44"/>
+      <c r="I32" s="101"/>
+      <c r="J32" s="101"/>
+      <c r="K32" s="101"/>
+      <c r="L32" s="101"/>
+      <c r="M32" s="101"/>
+      <c r="N32" s="101"/>
+      <c r="O32" s="101"/>
+      <c r="P32" s="101"/>
+      <c r="Q32" s="101"/>
+      <c r="R32" s="101"/>
+      <c r="S32" s="101"/>
+      <c r="T32" s="102"/>
+      <c r="U32" s="19"/>
+    </row>
+    <row r="33" spans="1:21" ht="4.9000000000000004" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="37"/>
+      <c r="B33" s="62"/>
+      <c r="C33" s="63"/>
+      <c r="D33" s="63"/>
+      <c r="E33" s="63"/>
+      <c r="F33" s="63"/>
+      <c r="G33" s="63"/>
+      <c r="H33" s="64"/>
+      <c r="I33" s="64"/>
+      <c r="J33" s="64"/>
+      <c r="K33" s="64"/>
+      <c r="L33" s="64"/>
+      <c r="M33" s="64"/>
+      <c r="N33" s="64"/>
+      <c r="O33" s="64"/>
+      <c r="P33" s="64"/>
+      <c r="Q33" s="64"/>
+      <c r="R33" s="64"/>
+      <c r="S33" s="64"/>
+      <c r="T33" s="65"/>
+      <c r="U33" s="20"/>
+    </row>
+    <row r="34" spans="1:21" s="7" customFormat="1" ht="15.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="66"/>
+      <c r="B34" s="67"/>
+      <c r="C34" s="107" t="s">
         <v>19</v>
       </c>
-      <c r="D33" s="107"/>
-      <c r="E33" s="107"/>
-      <c r="F33" s="107"/>
-      <c r="G33" s="107"/>
-      <c r="H33" s="107"/>
-      <c r="I33" s="107"/>
-      <c r="J33" s="107"/>
-      <c r="K33" s="107"/>
-      <c r="L33" s="107"/>
-      <c r="M33" s="107"/>
-      <c r="N33" s="107" t="s">
+      <c r="D34" s="107"/>
+      <c r="E34" s="107"/>
+      <c r="F34" s="107"/>
+      <c r="G34" s="107"/>
+      <c r="H34" s="107"/>
+      <c r="I34" s="107"/>
+      <c r="J34" s="107"/>
+      <c r="K34" s="107"/>
+      <c r="L34" s="107"/>
+      <c r="M34" s="107"/>
+      <c r="N34" s="107" t="s">
         <v>35</v>
       </c>
-      <c r="O33" s="107"/>
-      <c r="P33" s="107"/>
-      <c r="Q33" s="107"/>
-      <c r="R33" s="107"/>
-      <c r="S33" s="107"/>
-      <c r="T33" s="107"/>
-      <c r="U33" s="21"/>
-    </row>
-    <row r="34" spans="1:21" s="8" customFormat="1" ht="13.9" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="68"/>
-      <c r="B34" s="69"/>
-      <c r="C34" s="108" t="s">
+      <c r="O34" s="107"/>
+      <c r="P34" s="107"/>
+      <c r="Q34" s="107"/>
+      <c r="R34" s="107"/>
+      <c r="S34" s="107"/>
+      <c r="T34" s="107"/>
+      <c r="U34" s="21"/>
+    </row>
+    <row r="35" spans="1:21" s="8" customFormat="1" ht="13.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="68"/>
+      <c r="B35" s="69"/>
+      <c r="C35" s="108" t="s">
         <v>9</v>
       </c>
-      <c r="D34" s="108"/>
-      <c r="E34" s="108"/>
-      <c r="F34" s="108"/>
-      <c r="G34" s="108"/>
-      <c r="H34" s="108"/>
-      <c r="I34" s="108"/>
-      <c r="J34" s="108"/>
-      <c r="K34" s="108"/>
-      <c r="L34" s="108"/>
-      <c r="M34" s="108"/>
-      <c r="N34" s="108" t="s">
+      <c r="D35" s="108"/>
+      <c r="E35" s="108"/>
+      <c r="F35" s="108"/>
+      <c r="G35" s="108"/>
+      <c r="H35" s="108"/>
+      <c r="I35" s="108"/>
+      <c r="J35" s="108"/>
+      <c r="K35" s="108"/>
+      <c r="L35" s="108"/>
+      <c r="M35" s="108"/>
+      <c r="N35" s="108" t="s">
         <v>9</v>
       </c>
-      <c r="O34" s="108"/>
-      <c r="P34" s="108"/>
-      <c r="Q34" s="108"/>
-      <c r="R34" s="108"/>
-      <c r="S34" s="108"/>
-      <c r="T34" s="108"/>
-      <c r="U34" s="22"/>
-    </row>
-    <row r="35" spans="1:21" s="9" customFormat="1" ht="15.4" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="55"/>
-      <c r="B35" s="70"/>
-      <c r="C35" s="109" t="s">
+      <c r="O35" s="108"/>
+      <c r="P35" s="108"/>
+      <c r="Q35" s="108"/>
+      <c r="R35" s="108"/>
+      <c r="S35" s="108"/>
+      <c r="T35" s="108"/>
+      <c r="U35" s="22"/>
+    </row>
+    <row r="36" spans="1:21" s="9" customFormat="1" ht="15.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="55"/>
+      <c r="B36" s="70"/>
+      <c r="C36" s="109" t="s">
         <v>10</v>
       </c>
-      <c r="D35" s="109"/>
-      <c r="E35" s="109"/>
-      <c r="F35" s="109"/>
-      <c r="G35" s="109"/>
-      <c r="H35" s="109"/>
-      <c r="I35" s="109"/>
-      <c r="J35" s="109"/>
-      <c r="K35" s="109"/>
-      <c r="L35" s="109"/>
-      <c r="M35" s="109"/>
-      <c r="N35" s="109" t="s">
+      <c r="D36" s="109"/>
+      <c r="E36" s="109"/>
+      <c r="F36" s="109"/>
+      <c r="G36" s="109"/>
+      <c r="H36" s="109"/>
+      <c r="I36" s="109"/>
+      <c r="J36" s="109"/>
+      <c r="K36" s="109"/>
+      <c r="L36" s="109"/>
+      <c r="M36" s="109"/>
+      <c r="N36" s="109" t="s">
         <v>10</v>
       </c>
-      <c r="O35" s="109"/>
-      <c r="P35" s="109"/>
-      <c r="Q35" s="109"/>
-      <c r="R35" s="109"/>
-      <c r="S35" s="109"/>
-      <c r="T35" s="109"/>
-      <c r="U35" s="23"/>
-    </row>
-    <row r="36" spans="1:21" ht="10.15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="37"/>
-      <c r="B36" s="42"/>
-      <c r="C36" s="42"/>
-      <c r="D36" s="42"/>
-      <c r="E36" s="42"/>
-      <c r="F36" s="42"/>
-      <c r="G36" s="42"/>
-      <c r="H36" s="42"/>
-      <c r="I36" s="42"/>
-      <c r="J36" s="42"/>
-      <c r="K36" s="42"/>
-      <c r="L36" s="42"/>
-      <c r="M36" s="42"/>
-      <c r="N36" s="42"/>
-      <c r="O36" s="42"/>
-      <c r="P36" s="42"/>
-      <c r="Q36" s="42"/>
-      <c r="R36" s="42"/>
-      <c r="S36" s="42"/>
-      <c r="T36" s="42"/>
-      <c r="U36" s="24"/>
-    </row>
-    <row r="37" spans="1:21" ht="16.5" x14ac:dyDescent="0.25">
+      <c r="O36" s="109"/>
+      <c r="P36" s="109"/>
+      <c r="Q36" s="109"/>
+      <c r="R36" s="109"/>
+      <c r="S36" s="109"/>
+      <c r="T36" s="109"/>
+      <c r="U36" s="23"/>
+    </row>
+    <row r="37" spans="1:21" ht="10.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="37"/>
-      <c r="B37" s="38"/>
-      <c r="C37" s="38"/>
-      <c r="D37" s="38"/>
-      <c r="E37" s="38"/>
-      <c r="F37" s="38"/>
-      <c r="G37" s="38"/>
+      <c r="B37" s="42"/>
+      <c r="C37" s="42"/>
+      <c r="D37" s="42"/>
+      <c r="E37" s="42"/>
+      <c r="F37" s="42"/>
+      <c r="G37" s="42"/>
       <c r="H37" s="42"/>
       <c r="I37" s="42"/>
       <c r="J37" s="42"/>
       <c r="K37" s="42"/>
       <c r="L37" s="42"/>
-      <c r="M37" s="38"/>
-      <c r="N37" s="91" t="s">
+      <c r="M37" s="42"/>
+      <c r="N37" s="42"/>
+      <c r="O37" s="42"/>
+      <c r="P37" s="42"/>
+      <c r="Q37" s="42"/>
+      <c r="R37" s="42"/>
+      <c r="S37" s="42"/>
+      <c r="T37" s="42"/>
+      <c r="U37" s="24"/>
+    </row>
+    <row r="38" spans="1:21" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A38" s="37"/>
+      <c r="B38" s="38"/>
+      <c r="C38" s="38"/>
+      <c r="D38" s="38"/>
+      <c r="E38" s="38"/>
+      <c r="F38" s="38"/>
+      <c r="G38" s="38"/>
+      <c r="H38" s="42"/>
+      <c r="I38" s="42"/>
+      <c r="J38" s="42"/>
+      <c r="K38" s="42"/>
+      <c r="L38" s="42"/>
+      <c r="M38" s="38"/>
+      <c r="N38" s="91" t="s">
         <v>12</v>
       </c>
-      <c r="O37" s="71"/>
-      <c r="P37" s="71"/>
-      <c r="Q37" s="124"/>
-      <c r="R37" s="124"/>
-      <c r="S37" s="124"/>
-      <c r="T37" s="125"/>
-      <c r="U37" s="25"/>
-    </row>
-    <row r="38" spans="1:21" s="10" customFormat="1" ht="22.15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="72"/>
-      <c r="B38" s="73"/>
-      <c r="C38" s="73"/>
-      <c r="D38" s="73"/>
-      <c r="E38" s="73"/>
-      <c r="F38" s="73"/>
-      <c r="G38" s="73"/>
-      <c r="H38" s="74"/>
-      <c r="I38" s="74"/>
-      <c r="J38" s="74"/>
-      <c r="K38" s="74"/>
-      <c r="L38" s="74"/>
-      <c r="M38" s="73"/>
-      <c r="N38" s="103" t="s">
+      <c r="O38" s="71"/>
+      <c r="P38" s="71"/>
+      <c r="Q38" s="126"/>
+      <c r="R38" s="126"/>
+      <c r="S38" s="126"/>
+      <c r="T38" s="127"/>
+      <c r="U38" s="25"/>
+    </row>
+    <row r="39" spans="1:21" s="10" customFormat="1" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="72"/>
+      <c r="B39" s="73"/>
+      <c r="C39" s="73"/>
+      <c r="D39" s="73"/>
+      <c r="E39" s="73"/>
+      <c r="F39" s="73"/>
+      <c r="G39" s="73"/>
+      <c r="H39" s="74"/>
+      <c r="I39" s="74"/>
+      <c r="J39" s="74"/>
+      <c r="K39" s="74"/>
+      <c r="L39" s="74"/>
+      <c r="M39" s="73"/>
+      <c r="N39" s="103" t="s">
         <v>41</v>
       </c>
-      <c r="O38" s="104"/>
-      <c r="P38" s="104"/>
-      <c r="Q38" s="105"/>
-      <c r="R38" s="105"/>
-      <c r="S38" s="105"/>
-      <c r="T38" s="106"/>
-      <c r="U38" s="26"/>
-    </row>
-    <row r="39" spans="1:21" ht="13.15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="37"/>
-      <c r="B39" s="75"/>
-      <c r="C39" s="38"/>
-      <c r="D39" s="38"/>
-      <c r="E39" s="38"/>
-      <c r="F39" s="38"/>
-      <c r="G39" s="38"/>
-      <c r="H39" s="42"/>
-      <c r="I39" s="42"/>
-      <c r="J39" s="42" t="s">
-        <v>46</v>
-      </c>
-      <c r="K39" s="42"/>
-      <c r="L39" s="42"/>
-      <c r="M39" s="38"/>
-      <c r="N39" s="92" t="s">
-        <v>15</v>
-      </c>
-      <c r="O39" s="93"/>
-      <c r="P39" s="76"/>
-      <c r="Q39" s="97"/>
-      <c r="R39" s="97"/>
-      <c r="S39" s="97"/>
-      <c r="T39" s="98"/>
-      <c r="U39" s="27"/>
-    </row>
-    <row r="40" spans="1:21" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="O39" s="104"/>
+      <c r="P39" s="104"/>
+      <c r="Q39" s="105"/>
+      <c r="R39" s="105"/>
+      <c r="S39" s="105"/>
+      <c r="T39" s="106"/>
+      <c r="U39" s="26"/>
+    </row>
+    <row r="40" spans="1:21" ht="13.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="37"/>
-      <c r="B40" s="77"/>
-      <c r="C40" s="78"/>
-      <c r="D40" s="78"/>
-      <c r="E40" s="78"/>
-      <c r="F40" s="78"/>
-      <c r="G40" s="78"/>
+      <c r="B40" s="75"/>
+      <c r="C40" s="38"/>
+      <c r="D40" s="38"/>
+      <c r="E40" s="38"/>
+      <c r="F40" s="38"/>
+      <c r="G40" s="38"/>
       <c r="H40" s="42"/>
       <c r="I40" s="42"/>
-      <c r="J40" s="42"/>
+      <c r="J40" s="42" t="s">
+        <v>46</v>
+      </c>
       <c r="K40" s="42"/>
       <c r="L40" s="42"/>
-      <c r="M40" s="42"/>
-      <c r="N40" s="42"/>
-      <c r="O40" s="42"/>
-      <c r="P40" s="42"/>
-      <c r="Q40" s="42"/>
-      <c r="R40" s="42"/>
-      <c r="S40" s="42"/>
-      <c r="T40" s="42"/>
-      <c r="U40" s="24"/>
-    </row>
-    <row r="41" spans="1:21" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M40" s="38"/>
+      <c r="N40" s="92" t="s">
+        <v>15</v>
+      </c>
+      <c r="O40" s="93"/>
+      <c r="P40" s="76"/>
+      <c r="Q40" s="97"/>
+      <c r="R40" s="97"/>
+      <c r="S40" s="97"/>
+      <c r="T40" s="98"/>
+      <c r="U40" s="27"/>
+    </row>
+    <row r="41" spans="1:21" ht="7.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="37"/>
-      <c r="B41" s="79" t="s">
-        <v>34</v>
-      </c>
-      <c r="C41" s="80"/>
-      <c r="D41" s="80"/>
-      <c r="E41" s="80"/>
-      <c r="F41" s="80"/>
-      <c r="G41" s="80"/>
-      <c r="H41" s="143" t="s">
-        <v>50</v>
-      </c>
-      <c r="I41" s="142"/>
-      <c r="J41" s="142"/>
-      <c r="K41" s="142"/>
-      <c r="L41" s="96"/>
-      <c r="M41" s="38"/>
-      <c r="N41" s="77"/>
+      <c r="B41" s="77"/>
+      <c r="C41" s="78"/>
+      <c r="D41" s="78"/>
+      <c r="E41" s="78"/>
+      <c r="F41" s="78"/>
+      <c r="G41" s="78"/>
+      <c r="H41" s="42"/>
+      <c r="I41" s="42"/>
+      <c r="J41" s="42"/>
+      <c r="K41" s="42"/>
+      <c r="L41" s="42"/>
+      <c r="M41" s="42"/>
+      <c r="N41" s="42"/>
       <c r="O41" s="42"/>
       <c r="P41" s="42"/>
       <c r="Q41" s="42"/>
@@ -3384,23 +3383,23 @@
       <c r="T41" s="42"/>
       <c r="U41" s="24"/>
     </row>
-    <row r="42" spans="1:21" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:21" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="37"/>
-      <c r="B42" s="38" t="s">
-        <v>48</v>
-      </c>
-      <c r="C42" s="38"/>
-      <c r="D42" s="38"/>
-      <c r="E42" s="38"/>
-      <c r="F42" s="38"/>
-      <c r="G42" s="38"/>
-      <c r="H42" s="38"/>
-      <c r="I42" s="77" t="s">
-        <v>49</v>
-      </c>
-      <c r="J42" s="38"/>
-      <c r="K42" s="38"/>
-      <c r="L42" s="38"/>
+      <c r="B42" s="79" t="s">
+        <v>34</v>
+      </c>
+      <c r="C42" s="80"/>
+      <c r="D42" s="80"/>
+      <c r="E42" s="80"/>
+      <c r="F42" s="80"/>
+      <c r="G42" s="80"/>
+      <c r="H42" s="110" t="s">
+        <v>50</v>
+      </c>
+      <c r="I42" s="111"/>
+      <c r="J42" s="111"/>
+      <c r="K42" s="111"/>
+      <c r="L42" s="96"/>
       <c r="M42" s="38"/>
       <c r="N42" s="77"/>
       <c r="O42" s="42"/>
@@ -3411,116 +3410,142 @@
       <c r="T42" s="42"/>
       <c r="U42" s="24"/>
     </row>
-    <row r="43" spans="1:21" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="81"/>
-      <c r="B43" s="99" t="s">
+    <row r="43" spans="1:21" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="37"/>
+      <c r="B43" s="38" t="s">
+        <v>48</v>
+      </c>
+      <c r="C43" s="38"/>
+      <c r="D43" s="38"/>
+      <c r="E43" s="38"/>
+      <c r="F43" s="38"/>
+      <c r="G43" s="38"/>
+      <c r="H43" s="38"/>
+      <c r="I43" s="77" t="s">
+        <v>49</v>
+      </c>
+      <c r="J43" s="38"/>
+      <c r="K43" s="38"/>
+      <c r="L43" s="38"/>
+      <c r="M43" s="38"/>
+      <c r="N43" s="77"/>
+      <c r="O43" s="42"/>
+      <c r="P43" s="42"/>
+      <c r="Q43" s="42"/>
+      <c r="R43" s="42"/>
+      <c r="S43" s="42"/>
+      <c r="T43" s="42"/>
+      <c r="U43" s="24"/>
+    </row>
+    <row r="44" spans="1:21" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A44" s="81"/>
+      <c r="B44" s="99" t="s">
         <v>11</v>
       </c>
-      <c r="C43" s="99"/>
-      <c r="D43" s="99"/>
-      <c r="E43" s="99"/>
-      <c r="F43" s="99"/>
-      <c r="G43" s="99"/>
-      <c r="H43" s="99"/>
-      <c r="I43" s="99"/>
-      <c r="J43" s="99"/>
-      <c r="K43" s="99"/>
-      <c r="L43" s="99"/>
-      <c r="M43" s="99"/>
-      <c r="N43" s="99"/>
-      <c r="O43" s="99"/>
-      <c r="P43" s="99"/>
-      <c r="Q43" s="99"/>
-      <c r="R43" s="99"/>
-      <c r="S43" s="99"/>
-      <c r="T43" s="99"/>
-      <c r="U43" s="28"/>
-    </row>
-    <row r="44" spans="1:21" ht="12" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="38"/>
-      <c r="B44" s="100" t="s">
+      <c r="C44" s="99"/>
+      <c r="D44" s="99"/>
+      <c r="E44" s="99"/>
+      <c r="F44" s="99"/>
+      <c r="G44" s="99"/>
+      <c r="H44" s="99"/>
+      <c r="I44" s="99"/>
+      <c r="J44" s="99"/>
+      <c r="K44" s="99"/>
+      <c r="L44" s="99"/>
+      <c r="M44" s="99"/>
+      <c r="N44" s="99"/>
+      <c r="O44" s="99"/>
+      <c r="P44" s="99"/>
+      <c r="Q44" s="99"/>
+      <c r="R44" s="99"/>
+      <c r="S44" s="99"/>
+      <c r="T44" s="99"/>
+      <c r="U44" s="28"/>
+    </row>
+    <row r="45" spans="1:21" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="38"/>
+      <c r="B45" s="100" t="s">
         <v>47</v>
       </c>
-      <c r="C44" s="100"/>
-      <c r="D44" s="100"/>
-      <c r="E44" s="100"/>
-      <c r="F44" s="100"/>
-      <c r="G44" s="100"/>
-      <c r="H44" s="100"/>
-      <c r="I44" s="100"/>
-      <c r="J44" s="100"/>
-      <c r="K44" s="100"/>
-      <c r="L44" s="100"/>
-      <c r="M44" s="100"/>
-      <c r="N44" s="100"/>
-      <c r="O44" s="100"/>
-      <c r="P44" s="100"/>
-      <c r="Q44" s="100"/>
-      <c r="R44" s="100"/>
-      <c r="S44" s="100"/>
-      <c r="T44" s="100"/>
-      <c r="U44" s="2"/>
+      <c r="C45" s="100"/>
+      <c r="D45" s="100"/>
+      <c r="E45" s="100"/>
+      <c r="F45" s="100"/>
+      <c r="G45" s="100"/>
+      <c r="H45" s="100"/>
+      <c r="I45" s="100"/>
+      <c r="J45" s="100"/>
+      <c r="K45" s="100"/>
+      <c r="L45" s="100"/>
+      <c r="M45" s="100"/>
+      <c r="N45" s="100"/>
+      <c r="O45" s="100"/>
+      <c r="P45" s="100"/>
+      <c r="Q45" s="100"/>
+      <c r="R45" s="100"/>
+      <c r="S45" s="100"/>
+      <c r="T45" s="100"/>
+      <c r="U45" s="2"/>
     </row>
   </sheetData>
-  <mergeCells count="58">
-    <mergeCell ref="H9:T9"/>
-    <mergeCell ref="H10:T10"/>
-    <mergeCell ref="H11:T11"/>
-    <mergeCell ref="H12:L12"/>
+  <mergeCells count="57">
+    <mergeCell ref="H6:N6"/>
+    <mergeCell ref="H8:O8"/>
+    <mergeCell ref="B5:T5"/>
     <mergeCell ref="H2:O2"/>
     <mergeCell ref="P2:S2"/>
     <mergeCell ref="H3:O3"/>
     <mergeCell ref="P3:S3"/>
     <mergeCell ref="H4:O4"/>
-    <mergeCell ref="H5:N5"/>
-    <mergeCell ref="H7:O7"/>
-    <mergeCell ref="H13:J13"/>
-    <mergeCell ref="K13:T13"/>
-    <mergeCell ref="H14:J14"/>
-    <mergeCell ref="K14:T14"/>
-    <mergeCell ref="C24:K24"/>
-    <mergeCell ref="M24:O24"/>
-    <mergeCell ref="P24:R24"/>
-    <mergeCell ref="S24:T24"/>
-    <mergeCell ref="E19:T19"/>
-    <mergeCell ref="J21:L21"/>
-    <mergeCell ref="H17:T17"/>
+    <mergeCell ref="H18:T18"/>
+    <mergeCell ref="H14:T14"/>
+    <mergeCell ref="H15:T15"/>
+    <mergeCell ref="H10:T10"/>
+    <mergeCell ref="H11:T11"/>
+    <mergeCell ref="H12:T12"/>
+    <mergeCell ref="H13:L13"/>
     <mergeCell ref="C25:K25"/>
     <mergeCell ref="M25:O25"/>
     <mergeCell ref="P25:R25"/>
     <mergeCell ref="S25:T25"/>
+    <mergeCell ref="E20:T20"/>
+    <mergeCell ref="J22:L22"/>
     <mergeCell ref="C26:K26"/>
     <mergeCell ref="M26:O26"/>
     <mergeCell ref="P26:R26"/>
     <mergeCell ref="S26:T26"/>
-    <mergeCell ref="L30:R30"/>
-    <mergeCell ref="S30:T30"/>
-    <mergeCell ref="L28:R28"/>
-    <mergeCell ref="S28:T28"/>
-    <mergeCell ref="Q37:T37"/>
-    <mergeCell ref="J33:M33"/>
-    <mergeCell ref="N33:T33"/>
+    <mergeCell ref="C27:K27"/>
+    <mergeCell ref="M27:O27"/>
+    <mergeCell ref="P27:R27"/>
+    <mergeCell ref="S27:T27"/>
+    <mergeCell ref="L31:R31"/>
+    <mergeCell ref="S31:T31"/>
+    <mergeCell ref="L29:R29"/>
+    <mergeCell ref="S29:T29"/>
+    <mergeCell ref="Q38:T38"/>
     <mergeCell ref="J34:M34"/>
     <mergeCell ref="N34:T34"/>
     <mergeCell ref="J35:M35"/>
     <mergeCell ref="N35:T35"/>
-    <mergeCell ref="C27:K27"/>
-    <mergeCell ref="M27:O27"/>
-    <mergeCell ref="P27:R27"/>
-    <mergeCell ref="S27:T27"/>
-    <mergeCell ref="B29:H29"/>
-    <mergeCell ref="L29:R29"/>
-    <mergeCell ref="S29:T29"/>
+    <mergeCell ref="J36:M36"/>
+    <mergeCell ref="N36:T36"/>
+    <mergeCell ref="C28:K28"/>
+    <mergeCell ref="M28:O28"/>
+    <mergeCell ref="P28:R28"/>
+    <mergeCell ref="S28:T28"/>
+    <mergeCell ref="B30:H30"/>
+    <mergeCell ref="L30:R30"/>
+    <mergeCell ref="S30:T30"/>
+    <mergeCell ref="Q40:T40"/>
+    <mergeCell ref="B44:T44"/>
+    <mergeCell ref="B45:T45"/>
+    <mergeCell ref="I32:T32"/>
+    <mergeCell ref="N39:P39"/>
     <mergeCell ref="Q39:T39"/>
-    <mergeCell ref="B43:T43"/>
-    <mergeCell ref="B44:T44"/>
-    <mergeCell ref="I31:T31"/>
-    <mergeCell ref="N38:P38"/>
-    <mergeCell ref="Q38:T38"/>
-    <mergeCell ref="C33:I33"/>
     <mergeCell ref="C34:I34"/>
     <mergeCell ref="C35:I35"/>
-    <mergeCell ref="H41:K41"/>
+    <mergeCell ref="C36:I36"/>
+    <mergeCell ref="H42:K42"/>
   </mergeCells>
   <pageMargins left="0.3" right="0.2" top="0.5" bottom="0" header="0.25" footer="0"/>
   <pageSetup paperSize="9" scale="96" orientation="portrait" r:id="rId1"/>
